--- a/raw/Concepts.xlsx
+++ b/raw/Concepts.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="1641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="1659">
   <si>
     <t>id</t>
   </si>
@@ -117,7 +117,7 @@
 "bound form = A morpheme that may not stand on its own and must be attached to a stem." (Aronoff &amp; Fudeman 2011: 260) ——</t>
   </si>
   <si>
-    <t>haspelmath_bound_2021; blomfield_language_1933; lyons_introduction_1968; haspelmath_types_2023</t>
+    <t>haspelmath_bound_2021; bloomfield_language_1933; lyons_introduction_1968; haspelmath_types_2023</t>
   </si>
   <si>
     <t>second (clause) position</t>
@@ -834,7 +834,7 @@
     <t>STNEGC</t>
   </si>
   <si>
-    <t>A standard negation construction is a clausal construction with a negated verbal predicate in a declarative independent clause.</t>
+    <t>A standard negation construction is a clausal construction with a negated verbal predicate in a declarative non-subordinate clause.</t>
   </si>
   <si>
     <t>locational adverbial</t>
@@ -1823,6 +1823,19 @@
   </si>
   <si>
     <t>serial verb construction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A serial verb construction is a monoclausal construction consisting of multiple independent verbs with no element linking them and with no semantic predicate–argument relation between the verbs. </t>
+  </si>
+  <si>
+    <t>The definition is from Haspelmath (2016: 296), where it is discussed in detail (see also Haspelmath 2027).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“In many languages of the world, a sequence of several verbs act together as one unit. They form one predicate, and contain no overt marker of coordination, subordination, or syntactic dependency of any other sort. Such series of verbs are known as serial verb constructions, or serial verbs for short. Serial verbs describe what can be conceptualized as a single event. They are often pronounced as if they were one word.” (Aikhenvald 2018: 1)
+</t>
+  </si>
+  <si>
+    <t>haspelmath_serial_2016; haspelmath_biverbal_2027; aikhenvald_serial_2018</t>
   </si>
   <si>
     <t>dominant order</t>
@@ -2658,6 +2671,12 @@
     <t>antipassive voice construction</t>
   </si>
   <si>
+    <t xml:space="preserve">An antipassive voice construction is the coded alternant in an antipassive voice alternation. </t>
+  </si>
+  <si>
+    <t>The definition is from Haspelmath (2027). It is completely parallel to the definition of "passive (voice construction)".</t>
+  </si>
+  <si>
     <t>antipassive construction (CXN)</t>
   </si>
   <si>
@@ -2665,6 +2684,9 @@
 </t>
   </si>
   <si>
+    <t>haspelmath_antipassive_2027</t>
+  </si>
+  <si>
     <t>nonverbal clause construction</t>
   </si>
   <si>
@@ -2754,6 +2776,9 @@
 </t>
   </si>
   <si>
+    <t>The definition is from Haspelmath (2027). It does not define "auxiliary" as a kind of verb, but it requires the presence of subject indexing in order to distinguish auxiliaries from verb-associated particles. It does not make reference to a continuum or to grammaticalization, but defines an auxiliary as a bound form that is not an affix (i.e. a clitic).</t>
+  </si>
+  <si>
     <t>auxiliary verb</t>
   </si>
   <si>
@@ -2763,12 +2788,18 @@
     <t>auxiliary (CXN)</t>
   </si>
   <si>
-    <t xml:space="preserve">auxiliary (CXN) = the element expressing TAMP meaning in an auxiliary construction. [Example: in The cats have eaten, have is the auxiliary in the auxiliary construction have eaten.] (Section 13.4) ///
-auxiliary construction (CXN) = an eventive complex predicate construction in which one element of the construction, the auxiliary, denotes tense, aspect, modality, and/ or polarity (typically abbreviated TAMP), and the other element of the construction denotes the event whose tense, aspect, modality, and/or polarity is expressed by the first element. [Example: in English She might be sitting in the living room, might be sitting is an example of an auxiliary construction.] (Section 13.4) 
+    <t>auxiliary (CXN) = the element expressing TAMP meaning in an auxiliary construction. [Example: in The cats have eaten, have is the auxiliary in the auxiliary construction have eaten.] (Section 13.4) ///
+auxiliary construction (CXN) = an eventive complex predicate construction in which one element of the construction, the auxiliary, denotes tense, aspect, modality, and/ or polarity (typically abbreviated TAMP), and the other element of the construction denotes the event whose tense, aspect, modality, and/or polarity is expressed by the first element. [Example: in English She might be sitting in the living room, might be sitting is an example of an auxiliary construction.] (Section 13.4)</t>
+  </si>
+  <si>
+    <t>Auxiliary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“(An auxiliary is) an item on the lexical verb–functional affix continuum, which tends to be at least somewhat semantically bleached, and grammaticalized to express one or more of a range of salient verbal categories, most typically aspectual and modal categories, but also not infrequently temporal, negative polarity, or voice categories.” (Anderson 2006: 4-5)
 </t>
   </si>
   <si>
-    <t>Auxiliary</t>
+    <t>haspelmath_biverbal_2027; anderson_auxiliary_2006</t>
   </si>
   <si>
     <t>converb</t>
@@ -2777,10 +2808,11 @@
     <t>CVB</t>
   </si>
   <si>
-    <t>A converb is a form consisting of a verb root and an affix that can be used in converbal clauses, but not in independent clauses, in relative clauses, or in complement clauses.</t>
-  </si>
-  <si>
-    <t>The definition here makes reference to "converbal clause", because this is the basic use of converbs. They may also occur in auxiliary-like monoclausal constructions in several languages.</t>
+    <t xml:space="preserve">A converb is a form that consists of a verb stem and a special affix but no subject person indexing and that can occur as the predicate of a subordinate clause that is neither a relative clause nor a complement clause.
+</t>
+  </si>
+  <si>
+    <t>The definition is from Haspelmath (2027). It is different from the definition in (1995) in that it does not make reference to the notions "nonfinite" and "adverb" or "adverbial", and in that it does not rely on a "main function". Instead of "nonfinite", it specifies the presence of a special affix and the absence of subject person indexing.</t>
   </si>
   <si>
     <t>https://en.wikipedia.org/wiki/Converb</t>
@@ -2796,6 +2828,9 @@
   </si>
   <si>
     <t>"A converb is defined here as a nonfinite verb form whose main function is to mark adverbial subordination. Another way of putting it is that converbs are verbal adverbs, just like participles are verbal adjectives." (Haspelmath 1995: 3)</t>
+  </si>
+  <si>
+    <t>haspelmath_biverbal_2027; haspelmath_converb_1995</t>
   </si>
   <si>
     <t>postposition</t>
@@ -3059,7 +3094,7 @@
 </t>
   </si>
   <si>
-    <t>haspelmath_nonverbal_2025; bickerton_roots_1981; croft_morphosyntax_ 2022; johanson_belonging_2019</t>
+    <t>haspelmath_nonverbal_2025; bickerton_roots_1981; croft_morphosyntax_2022; johanson_belonging_2019</t>
   </si>
   <si>
     <t>possessor (role)</t>
@@ -5105,6 +5140,28 @@
   </si>
   <si>
     <t>STAN</t>
+  </si>
+  <si>
+    <t>monoclausal construction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A monoclausal construction is a clausal construction that can have only one predicate negation, even if there are multiple predicate forms.  </t>
+  </si>
+  <si>
+    <t>The definition is from Haspelmath (2027).</t>
+  </si>
+  <si>
+    <t>haspelmath_biverbal_2027</t>
+  </si>
+  <si>
+    <t>antipassive voice alternation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In an antipassive voice alternation, the uncoded alternant is transitive (with A- and P-arguments), whereas in the coded alternant, the basic P is downgraded, and the basic A corresponds to S.
+</t>
+  </si>
+  <si>
+    <t>voice alternation</t>
   </si>
 </sst>
 </file>
@@ -7968,7 +8025,16 @@
         <v>583</v>
       </c>
       <c r="D127" t="s" s="9">
-        <v>47</v>
+        <v>584</v>
+      </c>
+      <c r="E127" t="s" s="10">
+        <v>585</v>
+      </c>
+      <c r="N127" t="s" s="19">
+        <v>586</v>
+      </c>
+      <c r="O127" t="s" s="20">
+        <v>587</v>
       </c>
     </row>
     <row r="128">
@@ -7976,13 +8042,13 @@
         <v>141</v>
       </c>
       <c r="B128" t="s" s="7">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C128" t="s" s="8">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="D128" t="s" s="9">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="129">
@@ -7990,10 +8056,10 @@
         <v>142</v>
       </c>
       <c r="B129" t="s" s="7">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="D129" t="s" s="9">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="130">
@@ -8001,40 +8067,40 @@
         <v>143</v>
       </c>
       <c r="B130" t="s" s="7">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C130" t="s" s="8">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D130" t="s" s="9">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="E130" t="s" s="10">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="F130" t="s" s="11">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="G130" t="s" s="12">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="J130" t="s" s="15">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="K130" t="s" s="16">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="L130" t="s" s="17">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="N130" t="s" s="19">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="O130" t="s" s="20">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="P130" t="s" s="21">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="131">
@@ -8042,25 +8108,25 @@
         <v>144</v>
       </c>
       <c r="B131" t="s" s="7">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C131" t="s" s="8">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="D131" t="s" s="9">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="E131" t="s" s="10">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="J131" t="s" s="15">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="K131" t="s" s="16">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="L131" t="s" s="17">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="132">
@@ -8068,22 +8134,22 @@
         <v>145</v>
       </c>
       <c r="B132" t="s" s="7">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C132" t="s" s="8">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D132" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J132" t="s" s="15">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="K132" t="s" s="16">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="P132" t="s" s="21">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="133">
@@ -8091,25 +8157,25 @@
         <v>149</v>
       </c>
       <c r="B133" t="s" s="7">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="C133" t="s" s="8">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="D133" t="s" s="9">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="E133" t="s" s="10">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="J133" t="s" s="15">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="K133" t="s" s="16">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="N133" t="s" s="19">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="134">
@@ -8117,28 +8183,28 @@
         <v>150</v>
       </c>
       <c r="B134" t="s" s="7">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D134" t="s" s="9">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="H134" t="s" s="13">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="I134" t="s" s="14">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="J134" t="s" s="15">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="K134" t="s" s="16">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="L134" t="s" s="17">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="N134" t="s" s="19">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="135">
@@ -8146,16 +8212,16 @@
         <v>151</v>
       </c>
       <c r="B135" t="s" s="7">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D135" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J135" t="s" s="15">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="K135" t="s" s="16">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="136">
@@ -8163,10 +8229,10 @@
         <v>152</v>
       </c>
       <c r="B136" t="s" s="7">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D136" t="s" s="9">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="137">
@@ -8174,13 +8240,13 @@
         <v>153</v>
       </c>
       <c r="B137" t="s" s="7">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D137" t="s" s="9">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E137" t="s" s="10">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="138">
@@ -8188,10 +8254,10 @@
         <v>154</v>
       </c>
       <c r="B138" t="s" s="7">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D138" t="s" s="9">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="139">
@@ -8199,16 +8265,16 @@
         <v>155</v>
       </c>
       <c r="B139" t="s" s="7">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D139" t="s" s="9">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E139" t="s" s="10">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="N139" t="s" s="19">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="140">
@@ -8216,28 +8282,28 @@
         <v>156</v>
       </c>
       <c r="B140" t="s" s="7">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C140" t="s" s="8">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D140" t="s" s="9">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E140" t="s" s="10">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="H140" t="s" s="13">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="I140" t="s" s="14">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="J140" t="s" s="15">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="K140" t="s" s="16">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="141">
@@ -8245,13 +8311,13 @@
         <v>157</v>
       </c>
       <c r="B141" t="s" s="7">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C141" t="s" s="8">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="D141" t="s" s="9">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="142">
@@ -8259,13 +8325,13 @@
         <v>158</v>
       </c>
       <c r="B142" t="s" s="7">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C142" t="s" s="8">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D142" t="s" s="9">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="143">
@@ -8273,13 +8339,13 @@
         <v>159</v>
       </c>
       <c r="B143" t="s" s="7">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C143" t="s" s="8">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="D143" t="s" s="9">
-        <v>656</v>
+        <v>660</v>
       </c>
     </row>
     <row r="144">
@@ -8287,13 +8353,13 @@
         <v>160</v>
       </c>
       <c r="B144" t="s" s="7">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C144" t="s" s="8">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="D144" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="145">
@@ -8301,13 +8367,13 @@
         <v>161</v>
       </c>
       <c r="B145" t="s" s="7">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C145" t="s" s="8">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="D145" t="s" s="9">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="146">
@@ -8315,10 +8381,10 @@
         <v>162</v>
       </c>
       <c r="B146" t="s" s="7">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="D146" t="s" s="9">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="147">
@@ -8326,13 +8392,13 @@
         <v>163</v>
       </c>
       <c r="B147" t="s" s="7">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="D147" t="s" s="9">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E147" t="s" s="10">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="148">
@@ -8340,16 +8406,16 @@
         <v>164</v>
       </c>
       <c r="B148" t="s" s="7">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D148" t="s" s="9">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E148" t="s" s="10">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="N148" t="s" s="19">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="149">
@@ -8357,10 +8423,10 @@
         <v>165</v>
       </c>
       <c r="B149" t="s" s="7">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C149" t="s" s="8">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="D149" t="s" s="9">
         <v>47</v>
@@ -8371,10 +8437,10 @@
         <v>166</v>
       </c>
       <c r="B150" t="s" s="7">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D150" t="s" s="9">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="151">
@@ -8382,13 +8448,13 @@
         <v>167</v>
       </c>
       <c r="B151" t="s" s="7">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D151" t="s" s="9">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="E151" t="s" s="10">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="152">
@@ -8396,19 +8462,19 @@
         <v>169</v>
       </c>
       <c r="B152" t="s" s="7">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C152" t="s" s="8">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D152" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F152" t="s" s="11">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="G152" t="s" s="12">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="153">
@@ -8416,7 +8482,7 @@
         <v>170</v>
       </c>
       <c r="B153" t="s" s="7">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="D153" t="s" s="9">
         <v>47</v>
@@ -8427,19 +8493,19 @@
         <v>171</v>
       </c>
       <c r="B154" t="s" s="7">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D154" t="s" s="9">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="E154" t="s" s="10">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="F154" t="s" s="11">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G154" t="s" s="12">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="155">
@@ -8447,16 +8513,16 @@
         <v>172</v>
       </c>
       <c r="B155" t="s" s="7">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C155" t="s" s="8">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D155" t="s" s="9">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E155" t="s" s="10">
-        <v>691</v>
+        <v>695</v>
       </c>
     </row>
     <row r="156">
@@ -8464,10 +8530,10 @@
         <v>173</v>
       </c>
       <c r="B156" t="s" s="7">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="D156" t="s" s="9">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="157">
@@ -8475,34 +8541,34 @@
         <v>174</v>
       </c>
       <c r="B157" t="s" s="7">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C157" t="s" s="8">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D157" t="s" s="9">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="E157" t="s" s="10">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="F157" t="s" s="11">
+        <v>702</v>
+      </c>
+      <c r="G157" t="s" s="12">
+        <v>703</v>
+      </c>
+      <c r="H157" t="s" s="13">
         <v>698</v>
       </c>
-      <c r="G157" t="s" s="12">
-        <v>699</v>
-      </c>
-      <c r="H157" t="s" s="13">
-        <v>694</v>
-      </c>
       <c r="I157" t="s" s="14">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="J157" t="s" s="15">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="K157" t="s" s="16">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="158">
@@ -8510,7 +8576,7 @@
         <v>175</v>
       </c>
       <c r="B158" t="s" s="7">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="D158" t="s" s="9">
         <v>47</v>
@@ -8521,7 +8587,7 @@
         <v>176</v>
       </c>
       <c r="B159" t="s" s="7">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="D159" t="s" s="9">
         <v>47</v>
@@ -8535,19 +8601,19 @@
         <v>177</v>
       </c>
       <c r="B160" t="s" s="7">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C160" t="s" s="8">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="D160" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F160" t="s" s="11">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="G160" t="s" s="12">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="161">
@@ -8555,37 +8621,37 @@
         <v>178</v>
       </c>
       <c r="B161" t="s" s="7">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="C161" t="s" s="8">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="D161" t="s" s="9">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="E161" t="s" s="10">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="F161" t="s" s="11">
+        <v>716</v>
+      </c>
+      <c r="G161" t="s" s="12">
+        <v>717</v>
+      </c>
+      <c r="H161" t="s" s="13">
         <v>712</v>
       </c>
-      <c r="G161" t="s" s="12">
-        <v>713</v>
-      </c>
-      <c r="H161" t="s" s="13">
-        <v>708</v>
-      </c>
       <c r="I161" t="s" s="14">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="L161" t="s" s="17">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="N161" t="s" s="19">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="O161" t="s" s="20">
-        <v>716</v>
+        <v>720</v>
       </c>
     </row>
     <row r="162">
@@ -8593,25 +8659,25 @@
         <v>179</v>
       </c>
       <c r="B162" t="s" s="7">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C162" t="s" s="8">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D162" t="s" s="9">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E162" t="s" s="10">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F162" t="s" s="11">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="G162" t="s" s="12">
+        <v>725</v>
+      </c>
+      <c r="L162" t="s" s="17">
         <v>721</v>
-      </c>
-      <c r="L162" t="s" s="17">
-        <v>717</v>
       </c>
     </row>
     <row r="163">
@@ -8619,25 +8685,25 @@
         <v>180</v>
       </c>
       <c r="B163" t="s" s="7">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C163" t="s" s="8">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="D163" t="s" s="9">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E163" t="s" s="10">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="H163" t="s" s="13">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="I163" t="s" s="14">
+        <v>730</v>
+      </c>
+      <c r="L163" t="s" s="17">
         <v>726</v>
-      </c>
-      <c r="L163" t="s" s="17">
-        <v>722</v>
       </c>
     </row>
     <row r="164">
@@ -8645,16 +8711,16 @@
         <v>181</v>
       </c>
       <c r="B164" t="s" s="7">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C164" t="s" s="8">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="D164" t="s" s="9">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="L164" t="s" s="17">
-        <v>727</v>
+        <v>731</v>
       </c>
     </row>
     <row r="165">
@@ -8662,22 +8728,22 @@
         <v>182</v>
       </c>
       <c r="B165" t="s" s="7">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C165" t="s" s="8">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="D165" t="s" s="9">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="F165" t="s" s="11">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="G165" t="s" s="12">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="L165" t="s" s="17">
-        <v>730</v>
+        <v>734</v>
       </c>
     </row>
     <row r="166">
@@ -8685,22 +8751,22 @@
         <v>183</v>
       </c>
       <c r="B166" t="s" s="7">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C166" t="s" s="8">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="D166" t="s" s="9">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="F166" t="s" s="11">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="G166" t="s" s="12">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="L166" t="s" s="17">
-        <v>734</v>
+        <v>738</v>
       </c>
     </row>
     <row r="167">
@@ -8708,16 +8774,16 @@
         <v>184</v>
       </c>
       <c r="B167" t="s" s="7">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C167" t="s" s="8">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="D167" t="s" s="9">
         <v>47</v>
       </c>
       <c r="L167" t="s" s="17">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="168">
@@ -8725,34 +8791,34 @@
         <v>185</v>
       </c>
       <c r="B168" t="s" s="7">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C168" t="s" s="8">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="D168" t="s" s="9">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E168" t="s" s="10">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="F168" t="s" s="11">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="G168" t="s" s="12">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="H168" t="s" s="13">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="I168" t="s" s="14">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="L168" t="s" s="17">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="N168" t="s" s="19">
-        <v>749</v>
+        <v>753</v>
       </c>
     </row>
     <row r="169">
@@ -8760,19 +8826,19 @@
         <v>186</v>
       </c>
       <c r="B169" t="s" s="7">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="D169" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H169" t="s" s="13">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="I169" t="s" s="14">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="L169" t="s" s="17">
-        <v>751</v>
+        <v>755</v>
       </c>
     </row>
     <row r="170">
@@ -8780,19 +8846,19 @@
         <v>187</v>
       </c>
       <c r="B170" t="s" s="7">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="D170" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H170" t="s" s="13">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="I170" t="s" s="14">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="L170" t="s" s="17">
-        <v>754</v>
+        <v>758</v>
       </c>
     </row>
     <row r="171">
@@ -8800,19 +8866,19 @@
         <v>188</v>
       </c>
       <c r="B171" t="s" s="7">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="D171" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H171" t="s" s="13">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="I171" t="s" s="14">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="L171" t="s" s="17">
-        <v>757</v>
+        <v>761</v>
       </c>
     </row>
     <row r="172">
@@ -8820,7 +8886,7 @@
         <v>189</v>
       </c>
       <c r="B172" t="s" s="7">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="D172" t="s" s="9">
         <v>47</v>
@@ -8831,7 +8897,7 @@
         <v>190</v>
       </c>
       <c r="B173" t="s" s="7">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D173" t="s" s="9">
         <v>47</v>
@@ -8842,7 +8908,7 @@
         <v>191</v>
       </c>
       <c r="B174" t="s" s="7">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="D174" t="s" s="9">
         <v>47</v>
@@ -8853,10 +8919,10 @@
         <v>192</v>
       </c>
       <c r="B175" t="s" s="7">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="D175" t="s" s="9">
-        <v>763</v>
+        <v>767</v>
       </c>
     </row>
     <row r="176">
@@ -8864,13 +8930,13 @@
         <v>194</v>
       </c>
       <c r="B176" t="s" s="7">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="D176" t="s" s="9">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="E176" t="s" s="10">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="177">
@@ -8878,19 +8944,19 @@
         <v>195</v>
       </c>
       <c r="B177" t="s" s="7">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D177" t="s" s="9">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="H177" t="s" s="13">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="I177" t="s" s="14">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="N177" t="s" s="19">
-        <v>771</v>
+        <v>775</v>
       </c>
     </row>
     <row r="178">
@@ -8898,13 +8964,13 @@
         <v>196</v>
       </c>
       <c r="B178" t="s" s="7">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D178" t="s" s="9">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="N178" t="s" s="19">
-        <v>774</v>
+        <v>778</v>
       </c>
     </row>
     <row r="179">
@@ -8912,10 +8978,10 @@
         <v>197</v>
       </c>
       <c r="B179" t="s" s="7">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="D179" t="s" s="9">
-        <v>776</v>
+        <v>780</v>
       </c>
     </row>
     <row r="180">
@@ -8923,13 +8989,13 @@
         <v>198</v>
       </c>
       <c r="B180" t="s" s="7">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="D180" t="s" s="9">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="E180" t="s" s="10">
-        <v>779</v>
+        <v>783</v>
       </c>
     </row>
     <row r="181">
@@ -8937,13 +9003,13 @@
         <v>199</v>
       </c>
       <c r="B181" t="s" s="7">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="D181" t="s" s="9">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="E181" t="s" s="10">
-        <v>782</v>
+        <v>786</v>
       </c>
     </row>
     <row r="182">
@@ -8951,10 +9017,10 @@
         <v>200</v>
       </c>
       <c r="B182" t="s" s="7">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D182" t="s" s="9">
-        <v>784</v>
+        <v>788</v>
       </c>
     </row>
     <row r="183">
@@ -8962,16 +9028,16 @@
         <v>201</v>
       </c>
       <c r="B183" t="s" s="7">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="D183" t="s" s="9">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="H183" t="s" s="13">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="I183" t="s" s="14">
-        <v>787</v>
+        <v>791</v>
       </c>
     </row>
     <row r="184">
@@ -8979,16 +9045,16 @@
         <v>202</v>
       </c>
       <c r="B184" t="s" s="7">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="D184" t="s" s="9">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="E184" t="s" s="10">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="J184" t="s" s="15">
-        <v>791</v>
+        <v>795</v>
       </c>
     </row>
     <row r="185">
@@ -8996,16 +9062,16 @@
         <v>203</v>
       </c>
       <c r="B185" t="s" s="7">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C185" t="s" s="8">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D185" t="s" s="9">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="N185" t="s" s="19">
-        <v>795</v>
+        <v>799</v>
       </c>
     </row>
     <row r="186">
@@ -9013,7 +9079,7 @@
         <v>204</v>
       </c>
       <c r="B186" t="s" s="7">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="D186" t="s" s="9">
         <v>47</v>
@@ -9024,19 +9090,19 @@
         <v>205</v>
       </c>
       <c r="B187" t="s" s="7">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C187" t="s" s="8">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D187" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H187" t="s" s="13">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I187" t="s" s="14">
-        <v>800</v>
+        <v>804</v>
       </c>
     </row>
     <row r="188">
@@ -9044,10 +9110,10 @@
         <v>206</v>
       </c>
       <c r="B188" t="s" s="7">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C188" t="s" s="8">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="D188" t="s" s="9">
         <v>47</v>
@@ -9058,10 +9124,10 @@
         <v>207</v>
       </c>
       <c r="B189" t="s" s="7">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C189" t="s" s="8">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D189" t="s" s="9">
         <v>47</v>
@@ -9072,16 +9138,16 @@
         <v>208</v>
       </c>
       <c r="B190" t="s" s="7">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="D190" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H190" t="s" s="13">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I190" t="s" s="14">
-        <v>800</v>
+        <v>804</v>
       </c>
     </row>
     <row r="191">
@@ -9089,34 +9155,34 @@
         <v>209</v>
       </c>
       <c r="B191" t="s" s="7">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C191" t="s" s="8">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="D191" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F191" t="s" s="11">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="G191" t="s" s="12">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="H191" t="s" s="13">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="I191" t="s" s="14">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="J191" t="s" s="15">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="K191" t="s" s="16">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="L191" t="s" s="17">
-        <v>812</v>
+        <v>816</v>
       </c>
     </row>
     <row r="192">
@@ -9124,13 +9190,13 @@
         <v>210</v>
       </c>
       <c r="B192" t="s" s="7">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="C192" t="s" s="8">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="D192" t="s" s="9">
-        <v>815</v>
+        <v>819</v>
       </c>
     </row>
     <row r="193">
@@ -9138,10 +9204,10 @@
         <v>211</v>
       </c>
       <c r="B193" t="s" s="7">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D193" t="s" s="9">
-        <v>817</v>
+        <v>821</v>
       </c>
     </row>
     <row r="194">
@@ -9149,10 +9215,10 @@
         <v>212</v>
       </c>
       <c r="B194" t="s" s="7">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="D194" t="s" s="9">
-        <v>819</v>
+        <v>823</v>
       </c>
     </row>
     <row r="195">
@@ -9160,10 +9226,10 @@
         <v>213</v>
       </c>
       <c r="B195" t="s" s="7">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="D195" t="s" s="9">
-        <v>821</v>
+        <v>825</v>
       </c>
     </row>
     <row r="196">
@@ -9171,10 +9237,10 @@
         <v>214</v>
       </c>
       <c r="B196" t="s" s="7">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D196" t="s" s="9">
-        <v>823</v>
+        <v>827</v>
       </c>
     </row>
     <row r="197">
@@ -9182,10 +9248,10 @@
         <v>215</v>
       </c>
       <c r="B197" t="s" s="7">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="D197" t="s" s="9">
-        <v>825</v>
+        <v>829</v>
       </c>
     </row>
     <row r="198">
@@ -9193,10 +9259,10 @@
         <v>216</v>
       </c>
       <c r="B198" t="s" s="7">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D198" t="s" s="9">
-        <v>827</v>
+        <v>831</v>
       </c>
     </row>
     <row r="199">
@@ -9204,16 +9270,16 @@
         <v>217</v>
       </c>
       <c r="B199" t="s" s="7">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="C199" t="s" s="8">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="D199" t="s" s="9">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="E199" t="s" s="10">
-        <v>831</v>
+        <v>835</v>
       </c>
     </row>
     <row r="200">
@@ -9221,19 +9287,19 @@
         <v>218</v>
       </c>
       <c r="B200" t="s" s="7">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C200" t="s" s="8">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="D200" t="s" s="9">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="E200" t="s" s="10">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="N200" t="s" s="19">
-        <v>836</v>
+        <v>840</v>
       </c>
     </row>
     <row r="201">
@@ -9241,10 +9307,10 @@
         <v>219</v>
       </c>
       <c r="B201" t="s" s="7">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="D201" t="s" s="9">
-        <v>838</v>
+        <v>842</v>
       </c>
     </row>
     <row r="202">
@@ -9252,34 +9318,34 @@
         <v>220</v>
       </c>
       <c r="B202" t="s" s="7">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C202" t="s" s="8">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="D202" t="s" s="9">
         <v>47</v>
       </c>
       <c r="E202" t="s" s="10">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="F202" t="s" s="11">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="G202" t="s" s="12">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="J202" t="s" s="15">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="K202" t="s" s="16">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="N202" t="s" s="19">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="O202" t="s" s="20">
-        <v>847</v>
+        <v>851</v>
       </c>
     </row>
     <row r="203">
@@ -9287,16 +9353,22 @@
         <v>221</v>
       </c>
       <c r="B203" t="s" s="7">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="D203" t="s" s="9">
-        <v>47</v>
+        <v>853</v>
+      </c>
+      <c r="E203" t="s" s="10">
+        <v>854</v>
       </c>
       <c r="J203" t="s" s="15">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="K203" t="s" s="16">
-        <v>850</v>
+        <v>856</v>
+      </c>
+      <c r="O203" t="s" s="20">
+        <v>857</v>
       </c>
     </row>
     <row r="204">
@@ -9304,7 +9376,7 @@
         <v>222</v>
       </c>
       <c r="B204" t="s" s="7">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="D204" t="s" s="9">
         <v>47</v>
@@ -9315,10 +9387,10 @@
         <v>223</v>
       </c>
       <c r="B205" t="s" s="7">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="D205" t="s" s="9">
-        <v>853</v>
+        <v>860</v>
       </c>
     </row>
     <row r="206">
@@ -9326,16 +9398,16 @@
         <v>224</v>
       </c>
       <c r="B206" t="s" s="7">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="D206" t="s" s="9">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="N206" t="s" s="19">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="O206" t="s" s="20">
-        <v>857</v>
+        <v>864</v>
       </c>
     </row>
     <row r="207">
@@ -9343,7 +9415,7 @@
         <v>225</v>
       </c>
       <c r="B207" t="s" s="7">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="D207" t="s" s="9">
         <v>47</v>
@@ -9354,25 +9426,25 @@
         <v>226</v>
       </c>
       <c r="B208" t="s" s="7">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="D208" t="s" s="9">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="F208" t="s" s="11">
         <v>103</v>
       </c>
       <c r="G208" t="s" s="12">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="J208" t="s" s="15">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="K208" t="s" s="16">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="L208" t="s" s="17">
-        <v>864</v>
+        <v>871</v>
       </c>
     </row>
     <row r="209">
@@ -9380,19 +9452,19 @@
         <v>227</v>
       </c>
       <c r="B209" t="s" s="7">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="D209" t="s" s="9">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="F209" t="s" s="11">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="G209" t="s" s="12">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="L209" t="s" s="17">
-        <v>867</v>
+        <v>874</v>
       </c>
     </row>
     <row r="210">
@@ -9400,13 +9472,13 @@
         <v>228</v>
       </c>
       <c r="B210" t="s" s="7">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="D210" t="s" s="9">
         <v>47</v>
       </c>
       <c r="L210" t="s" s="17">
-        <v>869</v>
+        <v>876</v>
       </c>
     </row>
     <row r="211">
@@ -9414,22 +9486,22 @@
         <v>229</v>
       </c>
       <c r="B211" t="s" s="7">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="C211" t="s" s="8">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="D211" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H211" t="s" s="13">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I211" t="s" s="14">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="L211" t="s" s="17">
-        <v>874</v>
+        <v>881</v>
       </c>
     </row>
     <row r="212">
@@ -9437,13 +9509,13 @@
         <v>230</v>
       </c>
       <c r="B212" t="s" s="7">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="D212" t="s" s="9">
         <v>47</v>
       </c>
       <c r="L212" t="s" s="17">
-        <v>876</v>
+        <v>883</v>
       </c>
     </row>
     <row r="213">
@@ -9451,28 +9523,37 @@
         <v>231</v>
       </c>
       <c r="B213" t="s" s="7">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="C213" t="s" s="8">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="D213" t="s" s="9">
-        <v>879</v>
+        <v>886</v>
+      </c>
+      <c r="E213" t="s" s="10">
+        <v>887</v>
       </c>
       <c r="F213" t="s" s="11">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="G213" t="s" s="12">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="J213" t="s" s="15">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="K213" t="s" s="16">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="L213" t="s" s="17">
-        <v>884</v>
+        <v>892</v>
+      </c>
+      <c r="N213" t="s" s="19">
+        <v>893</v>
+      </c>
+      <c r="O213" t="s" s="20">
+        <v>894</v>
       </c>
     </row>
     <row r="214">
@@ -9480,34 +9561,37 @@
         <v>232</v>
       </c>
       <c r="B214" t="s" s="7">
-        <v>885</v>
+        <v>895</v>
       </c>
       <c r="C214" t="s" s="8">
-        <v>886</v>
+        <v>896</v>
       </c>
       <c r="D214" t="s" s="9">
-        <v>887</v>
+        <v>897</v>
       </c>
       <c r="E214" t="s" s="10">
-        <v>888</v>
+        <v>898</v>
       </c>
       <c r="F214" t="s" s="11">
-        <v>885</v>
+        <v>895</v>
       </c>
       <c r="G214" t="s" s="12">
-        <v>889</v>
+        <v>899</v>
       </c>
       <c r="J214" t="s" s="15">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="K214" t="s" s="16">
-        <v>891</v>
+        <v>901</v>
       </c>
       <c r="L214" t="s" s="17">
-        <v>892</v>
+        <v>902</v>
       </c>
       <c r="N214" t="s" s="19">
-        <v>893</v>
+        <v>903</v>
+      </c>
+      <c r="O214" t="s" s="20">
+        <v>904</v>
       </c>
     </row>
     <row r="215">
@@ -9515,28 +9599,28 @@
         <v>234</v>
       </c>
       <c r="B215" t="s" s="7">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="C215" t="s" s="8">
-        <v>895</v>
+        <v>906</v>
       </c>
       <c r="D215" t="s" s="9">
-        <v>896</v>
+        <v>907</v>
       </c>
       <c r="F215" t="s" s="11">
         <v>103</v>
       </c>
       <c r="G215" t="s" s="12">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="J215" t="s" s="15">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="K215" t="s" s="16">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="L215" t="s" s="17">
-        <v>899</v>
+        <v>910</v>
       </c>
     </row>
     <row r="216">
@@ -9544,19 +9628,19 @@
         <v>235</v>
       </c>
       <c r="B216" t="s" s="7">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="C216" t="s" s="8">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="D216" t="s" s="9">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="E216" t="s" s="10">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="L216" t="s" s="17">
-        <v>904</v>
+        <v>915</v>
       </c>
     </row>
     <row r="217">
@@ -9564,19 +9648,19 @@
         <v>236</v>
       </c>
       <c r="B217" t="s" s="7">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="D217" t="s" s="9">
         <v>47</v>
       </c>
       <c r="E217" t="s" s="10">
-        <v>906</v>
+        <v>917</v>
       </c>
       <c r="L217" t="s" s="17">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="N217" t="s" s="19">
-        <v>908</v>
+        <v>919</v>
       </c>
     </row>
     <row r="218">
@@ -9584,16 +9668,16 @@
         <v>238</v>
       </c>
       <c r="B218" t="s" s="7">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="D218" t="s" s="9">
         <v>47</v>
       </c>
       <c r="E218" t="s" s="10">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="L218" t="s" s="17">
-        <v>911</v>
+        <v>922</v>
       </c>
     </row>
     <row r="219">
@@ -9601,13 +9685,13 @@
         <v>239</v>
       </c>
       <c r="B219" t="s" s="7">
-        <v>912</v>
+        <v>923</v>
       </c>
       <c r="D219" t="s" s="9">
         <v>47</v>
       </c>
       <c r="L219" t="s" s="17">
-        <v>913</v>
+        <v>924</v>
       </c>
     </row>
     <row r="220">
@@ -9615,13 +9699,13 @@
         <v>240</v>
       </c>
       <c r="B220" t="s" s="7">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="D220" t="s" s="9">
         <v>47</v>
       </c>
       <c r="L220" t="s" s="17">
-        <v>915</v>
+        <v>926</v>
       </c>
     </row>
     <row r="221">
@@ -9629,16 +9713,16 @@
         <v>241</v>
       </c>
       <c r="B221" t="s" s="7">
-        <v>916</v>
+        <v>927</v>
       </c>
       <c r="D221" t="s" s="9">
-        <v>917</v>
+        <v>928</v>
       </c>
       <c r="E221" t="s" s="10">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="L221" t="s" s="17">
-        <v>919</v>
+        <v>930</v>
       </c>
     </row>
     <row r="222">
@@ -9646,31 +9730,31 @@
         <v>242</v>
       </c>
       <c r="B222" t="s" s="7">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="D222" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F222" t="s" s="11">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="G222" t="s" s="12">
-        <v>921</v>
+        <v>932</v>
       </c>
       <c r="H222" t="s" s="13">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="I222" t="s" s="14">
-        <v>922</v>
+        <v>933</v>
       </c>
       <c r="L222" t="s" s="17">
-        <v>923</v>
+        <v>934</v>
       </c>
       <c r="N222" t="s" s="19">
-        <v>924</v>
+        <v>935</v>
       </c>
       <c r="O222" t="s" s="20">
-        <v>925</v>
+        <v>936</v>
       </c>
     </row>
     <row r="223">
@@ -9678,13 +9762,13 @@
         <v>243</v>
       </c>
       <c r="B223" t="s" s="7">
-        <v>926</v>
+        <v>937</v>
       </c>
       <c r="D223" t="s" s="9">
         <v>47</v>
       </c>
       <c r="L223" t="s" s="17">
-        <v>927</v>
+        <v>938</v>
       </c>
     </row>
     <row r="224">
@@ -9692,16 +9776,16 @@
         <v>244</v>
       </c>
       <c r="B224" t="s" s="7">
-        <v>928</v>
+        <v>939</v>
       </c>
       <c r="D224" t="s" s="9">
         <v>47</v>
       </c>
       <c r="E224" t="s" s="10">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="L224" t="s" s="17">
-        <v>930</v>
+        <v>941</v>
       </c>
     </row>
     <row r="225">
@@ -9709,13 +9793,13 @@
         <v>245</v>
       </c>
       <c r="B225" t="s" s="7">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="D225" t="s" s="9">
         <v>47</v>
       </c>
       <c r="L225" t="s" s="17">
-        <v>932</v>
+        <v>943</v>
       </c>
     </row>
     <row r="226">
@@ -9729,7 +9813,7 @@
         <v>47</v>
       </c>
       <c r="L226" t="s" s="17">
-        <v>933</v>
+        <v>944</v>
       </c>
     </row>
     <row r="227">
@@ -9737,16 +9821,16 @@
         <v>247</v>
       </c>
       <c r="B227" t="s" s="7">
-        <v>934</v>
+        <v>945</v>
       </c>
       <c r="D227" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F227" t="s" s="11">
-        <v>935</v>
+        <v>946</v>
       </c>
       <c r="L227" t="s" s="17">
-        <v>936</v>
+        <v>947</v>
       </c>
     </row>
     <row r="228">
@@ -9754,16 +9838,16 @@
         <v>248</v>
       </c>
       <c r="B228" t="s" s="7">
-        <v>937</v>
+        <v>948</v>
       </c>
       <c r="C228" t="s" s="8">
-        <v>938</v>
+        <v>949</v>
       </c>
       <c r="D228" t="s" s="9">
         <v>47</v>
       </c>
       <c r="L228" t="s" s="17">
-        <v>939</v>
+        <v>950</v>
       </c>
     </row>
     <row r="229">
@@ -9771,16 +9855,16 @@
         <v>250</v>
       </c>
       <c r="B229" t="s" s="7">
-        <v>940</v>
+        <v>951</v>
       </c>
       <c r="D229" t="s" s="9">
-        <v>941</v>
+        <v>952</v>
       </c>
       <c r="F229" t="s" s="11">
         <v>103</v>
       </c>
       <c r="G229" t="s" s="12">
-        <v>942</v>
+        <v>953</v>
       </c>
     </row>
     <row r="230">
@@ -9788,7 +9872,7 @@
         <v>251</v>
       </c>
       <c r="B230" t="s" s="7">
-        <v>943</v>
+        <v>954</v>
       </c>
       <c r="D230" t="s" s="9">
         <v>47</v>
@@ -9797,19 +9881,19 @@
         <v>39</v>
       </c>
       <c r="H230" t="s" s="13">
-        <v>943</v>
+        <v>954</v>
       </c>
       <c r="I230" t="s" s="14">
-        <v>944</v>
+        <v>955</v>
       </c>
       <c r="J230" t="s" s="15">
-        <v>945</v>
+        <v>956</v>
       </c>
       <c r="K230" t="s" s="16">
-        <v>946</v>
+        <v>957</v>
       </c>
       <c r="L230" t="s" s="17">
-        <v>947</v>
+        <v>958</v>
       </c>
     </row>
     <row r="231">
@@ -9817,28 +9901,28 @@
         <v>252</v>
       </c>
       <c r="B231" t="s" s="7">
-        <v>948</v>
+        <v>959</v>
       </c>
       <c r="C231" t="s" s="8">
-        <v>949</v>
+        <v>960</v>
       </c>
       <c r="D231" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F231" t="s" s="11">
-        <v>948</v>
+        <v>959</v>
       </c>
       <c r="G231" t="s" s="12">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="H231" t="s" s="13">
-        <v>948</v>
+        <v>959</v>
       </c>
       <c r="I231" t="s" s="14">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="L231" t="s" s="17">
-        <v>952</v>
+        <v>963</v>
       </c>
     </row>
     <row r="232">
@@ -9846,28 +9930,28 @@
         <v>253</v>
       </c>
       <c r="B232" t="s" s="7">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="C232" t="s" s="8">
-        <v>954</v>
+        <v>965</v>
       </c>
       <c r="D232" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F232" t="s" s="11">
-        <v>955</v>
+        <v>966</v>
       </c>
       <c r="G232" t="s" s="12">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="H232" t="s" s="13">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="I232" t="s" s="14">
-        <v>957</v>
+        <v>968</v>
       </c>
       <c r="L232" t="s" s="17">
-        <v>958</v>
+        <v>969</v>
       </c>
     </row>
     <row r="233">
@@ -9875,28 +9959,28 @@
         <v>254</v>
       </c>
       <c r="B233" t="s" s="7">
-        <v>959</v>
+        <v>970</v>
       </c>
       <c r="C233" t="s" s="8">
-        <v>960</v>
+        <v>971</v>
       </c>
       <c r="D233" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F233" t="s" s="11">
-        <v>959</v>
+        <v>970</v>
       </c>
       <c r="G233" t="s" s="12">
-        <v>961</v>
+        <v>972</v>
       </c>
       <c r="J233" t="s" s="15">
-        <v>962</v>
+        <v>973</v>
       </c>
       <c r="K233" t="s" s="16">
-        <v>963</v>
+        <v>974</v>
       </c>
       <c r="L233" t="s" s="17">
-        <v>964</v>
+        <v>975</v>
       </c>
     </row>
     <row r="234">
@@ -9904,19 +9988,19 @@
         <v>255</v>
       </c>
       <c r="B234" t="s" s="7">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="C234" t="s" s="8">
-        <v>966</v>
+        <v>977</v>
       </c>
       <c r="D234" t="s" s="9">
         <v>47</v>
       </c>
       <c r="E234" t="s" s="10">
-        <v>967</v>
+        <v>978</v>
       </c>
       <c r="L234" t="s" s="17">
-        <v>968</v>
+        <v>979</v>
       </c>
     </row>
     <row r="235">
@@ -9924,19 +10008,19 @@
         <v>256</v>
       </c>
       <c r="B235" t="s" s="7">
-        <v>969</v>
+        <v>980</v>
       </c>
       <c r="D235" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J235" t="s" s="15">
-        <v>970</v>
+        <v>981</v>
       </c>
       <c r="K235" t="s" s="16">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="L235" t="s" s="17">
-        <v>972</v>
+        <v>983</v>
       </c>
     </row>
     <row r="236">
@@ -9944,13 +10028,13 @@
         <v>257</v>
       </c>
       <c r="B236" t="s" s="7">
-        <v>973</v>
+        <v>984</v>
       </c>
       <c r="D236" t="s" s="9">
-        <v>974</v>
+        <v>985</v>
       </c>
       <c r="E236" t="s" s="10">
-        <v>975</v>
+        <v>986</v>
       </c>
     </row>
     <row r="237">
@@ -9958,16 +10042,16 @@
         <v>259</v>
       </c>
       <c r="B237" t="s" s="7">
-        <v>976</v>
+        <v>987</v>
       </c>
       <c r="D237" t="s" s="9">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="E237" t="s" s="10">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="O237" t="s" s="20">
-        <v>979</v>
+        <v>990</v>
       </c>
     </row>
     <row r="238">
@@ -9975,16 +10059,16 @@
         <v>260</v>
       </c>
       <c r="B238" t="s" s="7">
-        <v>980</v>
+        <v>991</v>
       </c>
       <c r="D238" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J238" t="s" s="15">
-        <v>981</v>
+        <v>992</v>
       </c>
       <c r="K238" t="s" s="16">
-        <v>982</v>
+        <v>993</v>
       </c>
     </row>
     <row r="239">
@@ -9992,7 +10076,7 @@
         <v>261</v>
       </c>
       <c r="B239" t="s" s="7">
-        <v>983</v>
+        <v>994</v>
       </c>
       <c r="D239" t="s" s="9">
         <v>140</v>
@@ -10003,13 +10087,13 @@
         <v>262</v>
       </c>
       <c r="B240" t="s" s="7">
-        <v>984</v>
+        <v>995</v>
       </c>
       <c r="D240" t="s" s="9">
-        <v>985</v>
+        <v>996</v>
       </c>
       <c r="E240" t="s" s="10">
-        <v>986</v>
+        <v>997</v>
       </c>
     </row>
     <row r="241">
@@ -10017,10 +10101,10 @@
         <v>263</v>
       </c>
       <c r="B241" t="s" s="7">
-        <v>987</v>
+        <v>998</v>
       </c>
       <c r="D241" t="s" s="9">
-        <v>988</v>
+        <v>999</v>
       </c>
     </row>
     <row r="242">
@@ -10028,13 +10112,13 @@
         <v>264</v>
       </c>
       <c r="B242" t="s" s="7">
-        <v>989</v>
+        <v>1000</v>
       </c>
       <c r="D242" t="s" s="9">
-        <v>990</v>
+        <v>1001</v>
       </c>
       <c r="E242" t="s" s="10">
-        <v>991</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="243">
@@ -10042,10 +10126,10 @@
         <v>265</v>
       </c>
       <c r="B243" t="s" s="7">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="D243" t="s" s="9">
-        <v>993</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="244">
@@ -10053,7 +10137,7 @@
         <v>266</v>
       </c>
       <c r="B244" t="s" s="7">
-        <v>994</v>
+        <v>1005</v>
       </c>
       <c r="D244" t="s" s="9">
         <v>47</v>
@@ -10064,16 +10148,16 @@
         <v>267</v>
       </c>
       <c r="B245" t="s" s="7">
-        <v>995</v>
+        <v>1006</v>
       </c>
       <c r="D245" t="s" s="9">
-        <v>996</v>
+        <v>1007</v>
       </c>
       <c r="F245" t="s" s="11">
-        <v>997</v>
+        <v>1008</v>
       </c>
       <c r="G245" t="s" s="12">
-        <v>998</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="246">
@@ -10081,7 +10165,7 @@
         <v>268</v>
       </c>
       <c r="B246" t="s" s="7">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="D246" t="s" s="9">
         <v>140</v>
@@ -10092,7 +10176,7 @@
         <v>269</v>
       </c>
       <c r="B247" t="s" s="7">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="D247" t="s" s="9">
         <v>140</v>
@@ -10103,10 +10187,10 @@
         <v>270</v>
       </c>
       <c r="B248" t="s" s="7">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="D248" t="s" s="9">
-        <v>1002</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="249">
@@ -10114,7 +10198,7 @@
         <v>271</v>
       </c>
       <c r="B249" t="s" s="7">
-        <v>1003</v>
+        <v>1014</v>
       </c>
       <c r="D249" t="s" s="9">
         <v>47</v>
@@ -10125,13 +10209,13 @@
         <v>273</v>
       </c>
       <c r="B250" t="s" s="7">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="D250" t="s" s="9">
-        <v>1005</v>
+        <v>1016</v>
       </c>
       <c r="E250" t="s" s="10">
-        <v>1006</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="251">
@@ -10139,25 +10223,25 @@
         <v>274</v>
       </c>
       <c r="B251" t="s" s="7">
-        <v>1007</v>
+        <v>1018</v>
       </c>
       <c r="C251" t="s" s="8">
-        <v>1008</v>
+        <v>1019</v>
       </c>
       <c r="D251" t="s" s="9">
-        <v>1009</v>
+        <v>1020</v>
       </c>
       <c r="E251" t="s" s="10">
-        <v>1010</v>
+        <v>1021</v>
       </c>
       <c r="F251" t="s" s="11">
-        <v>1011</v>
+        <v>1022</v>
       </c>
       <c r="G251" t="s" s="12">
-        <v>1012</v>
+        <v>1023</v>
       </c>
       <c r="N251" t="s" s="19">
-        <v>1013</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="252">
@@ -10165,10 +10249,10 @@
         <v>275</v>
       </c>
       <c r="B252" t="s" s="7">
-        <v>1014</v>
+        <v>1025</v>
       </c>
       <c r="D252" t="s" s="9">
-        <v>1015</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="253">
@@ -10176,10 +10260,10 @@
         <v>276</v>
       </c>
       <c r="B253" t="s" s="7">
-        <v>1016</v>
+        <v>1027</v>
       </c>
       <c r="D253" t="s" s="9">
-        <v>1017</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="254">
@@ -10187,10 +10271,10 @@
         <v>277</v>
       </c>
       <c r="B254" t="s" s="7">
-        <v>1018</v>
+        <v>1029</v>
       </c>
       <c r="D254" t="s" s="9">
-        <v>1019</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="255">
@@ -10198,10 +10282,10 @@
         <v>278</v>
       </c>
       <c r="B255" t="s" s="7">
-        <v>1020</v>
+        <v>1031</v>
       </c>
       <c r="D255" t="s" s="9">
-        <v>1021</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="256">
@@ -10209,10 +10293,10 @@
         <v>279</v>
       </c>
       <c r="B256" t="s" s="7">
-        <v>1022</v>
+        <v>1033</v>
       </c>
       <c r="D256" t="s" s="9">
-        <v>1023</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="257">
@@ -10220,16 +10304,16 @@
         <v>280</v>
       </c>
       <c r="B257" t="s" s="7">
-        <v>1024</v>
+        <v>1035</v>
       </c>
       <c r="D257" t="s" s="9">
-        <v>1025</v>
+        <v>1036</v>
       </c>
       <c r="F257" t="s" s="11">
-        <v>1026</v>
+        <v>1037</v>
       </c>
       <c r="G257" t="s" s="12">
-        <v>1027</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="258">
@@ -10237,10 +10321,10 @@
         <v>281</v>
       </c>
       <c r="B258" t="s" s="7">
-        <v>1028</v>
+        <v>1039</v>
       </c>
       <c r="D258" t="s" s="9">
-        <v>1029</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="259">
@@ -10248,10 +10332,10 @@
         <v>282</v>
       </c>
       <c r="B259" t="s" s="7">
-        <v>1030</v>
+        <v>1041</v>
       </c>
       <c r="D259" t="s" s="9">
-        <v>1031</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="260">
@@ -10259,13 +10343,13 @@
         <v>283</v>
       </c>
       <c r="B260" t="s" s="7">
-        <v>1032</v>
+        <v>1043</v>
       </c>
       <c r="D260" t="s" s="9">
-        <v>1033</v>
+        <v>1044</v>
       </c>
       <c r="E260" t="s" s="10">
-        <v>1034</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="261">
@@ -10273,10 +10357,10 @@
         <v>284</v>
       </c>
       <c r="B261" t="s" s="7">
-        <v>1035</v>
+        <v>1046</v>
       </c>
       <c r="D261" t="s" s="9">
-        <v>1036</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="262">
@@ -10284,10 +10368,10 @@
         <v>285</v>
       </c>
       <c r="B262" t="s" s="7">
-        <v>1037</v>
+        <v>1048</v>
       </c>
       <c r="D262" t="s" s="9">
-        <v>1038</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="263">
@@ -10295,10 +10379,10 @@
         <v>286</v>
       </c>
       <c r="B263" t="s" s="7">
-        <v>1039</v>
+        <v>1050</v>
       </c>
       <c r="D263" t="s" s="9">
-        <v>1040</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="264">
@@ -10306,10 +10390,10 @@
         <v>287</v>
       </c>
       <c r="B264" t="s" s="7">
-        <v>1041</v>
+        <v>1052</v>
       </c>
       <c r="D264" t="s" s="9">
-        <v>1042</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="265">
@@ -10317,16 +10401,16 @@
         <v>289</v>
       </c>
       <c r="B265" t="s" s="7">
-        <v>1043</v>
+        <v>1054</v>
       </c>
       <c r="D265" t="s" s="9">
-        <v>1044</v>
+        <v>1055</v>
       </c>
       <c r="H265" t="s" s="13">
-        <v>1045</v>
+        <v>1056</v>
       </c>
       <c r="I265" t="s" s="14">
-        <v>1046</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="266">
@@ -10334,22 +10418,22 @@
         <v>290</v>
       </c>
       <c r="B266" t="s" s="7">
-        <v>1047</v>
+        <v>1058</v>
       </c>
       <c r="D266" t="s" s="9">
         <v>140</v>
       </c>
       <c r="F266" t="s" s="11">
-        <v>1048</v>
+        <v>1059</v>
       </c>
       <c r="G266" t="s" s="12">
-        <v>1049</v>
+        <v>1060</v>
       </c>
       <c r="J266" t="s" s="15">
-        <v>1050</v>
+        <v>1061</v>
       </c>
       <c r="K266" t="s" s="16">
-        <v>1051</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="267">
@@ -10357,10 +10441,10 @@
         <v>291</v>
       </c>
       <c r="B267" t="s" s="7">
-        <v>1052</v>
+        <v>1063</v>
       </c>
       <c r="D267" t="s" s="9">
-        <v>1053</v>
+        <v>1064</v>
       </c>
       <c r="F267" t="s" s="11">
         <v>39</v>
@@ -10371,25 +10455,25 @@
         <v>292</v>
       </c>
       <c r="B268" t="s" s="7">
-        <v>1054</v>
+        <v>1065</v>
       </c>
       <c r="D268" t="s" s="9">
-        <v>1055</v>
+        <v>1066</v>
       </c>
       <c r="F268" t="s" s="11">
         <v>39</v>
       </c>
       <c r="H268" t="s" s="13">
-        <v>1056</v>
+        <v>1067</v>
       </c>
       <c r="I268" t="s" s="14">
-        <v>1057</v>
+        <v>1068</v>
       </c>
       <c r="J268" t="s" s="15">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="K268" t="s" s="16">
-        <v>1059</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="269">
@@ -10397,16 +10481,16 @@
         <v>293</v>
       </c>
       <c r="B269" t="s" s="7">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="D269" t="s" s="9">
-        <v>1061</v>
+        <v>1072</v>
       </c>
       <c r="J269" t="s" s="15">
-        <v>1062</v>
+        <v>1073</v>
       </c>
       <c r="K269" t="s" s="16">
-        <v>1063</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="270">
@@ -10414,19 +10498,19 @@
         <v>294</v>
       </c>
       <c r="B270" t="s" s="7">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D270" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J270" t="s" s="15">
-        <v>1065</v>
+        <v>1076</v>
       </c>
       <c r="K270" t="s" s="16">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="P270" t="s" s="21">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="271">
@@ -10434,22 +10518,22 @@
         <v>295</v>
       </c>
       <c r="B271" t="s" s="7">
-        <v>1068</v>
+        <v>1079</v>
       </c>
       <c r="D271" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H271" t="s" s="13">
-        <v>1069</v>
+        <v>1080</v>
       </c>
       <c r="I271" t="s" s="14">
-        <v>1070</v>
+        <v>1081</v>
       </c>
       <c r="J271" t="s" s="15">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="K271" t="s" s="16">
-        <v>1072</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="272">
@@ -10457,10 +10541,10 @@
         <v>296</v>
       </c>
       <c r="B272" t="s" s="7">
-        <v>1073</v>
+        <v>1084</v>
       </c>
       <c r="C272" t="s" s="8">
-        <v>1074</v>
+        <v>1085</v>
       </c>
       <c r="D272" t="s" s="9">
         <v>47</v>
@@ -10469,10 +10553,10 @@
         <v>39</v>
       </c>
       <c r="J272" t="s" s="15">
-        <v>1075</v>
+        <v>1086</v>
       </c>
       <c r="K272" t="s" s="16">
-        <v>1076</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="273">
@@ -10480,19 +10564,19 @@
         <v>297</v>
       </c>
       <c r="B273" t="s" s="7">
-        <v>1077</v>
+        <v>1088</v>
       </c>
       <c r="D273" t="s" s="9">
-        <v>1078</v>
+        <v>1089</v>
       </c>
       <c r="E273" t="s" s="10">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="J273" t="s" s="15">
-        <v>1080</v>
+        <v>1091</v>
       </c>
       <c r="K273" t="s" s="16">
-        <v>1081</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="274">
@@ -10500,16 +10584,16 @@
         <v>298</v>
       </c>
       <c r="B274" t="s" s="7">
-        <v>1082</v>
+        <v>1093</v>
       </c>
       <c r="D274" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J274" t="s" s="15">
-        <v>1083</v>
+        <v>1094</v>
       </c>
       <c r="K274" t="s" s="16">
-        <v>1084</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="275">
@@ -10517,16 +10601,16 @@
         <v>299</v>
       </c>
       <c r="B275" t="s" s="7">
-        <v>1085</v>
+        <v>1096</v>
       </c>
       <c r="D275" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J275" t="s" s="15">
-        <v>1086</v>
+        <v>1097</v>
       </c>
       <c r="K275" t="s" s="16">
-        <v>1087</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="276">
@@ -10534,16 +10618,16 @@
         <v>300</v>
       </c>
       <c r="B276" t="s" s="7">
-        <v>1088</v>
+        <v>1099</v>
       </c>
       <c r="C276" t="s" s="8">
-        <v>1089</v>
+        <v>1100</v>
       </c>
       <c r="D276" t="s" s="9">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="E276" t="s" s="10">
-        <v>1091</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="277">
@@ -10551,16 +10635,16 @@
         <v>301</v>
       </c>
       <c r="B277" t="s" s="7">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="D277" t="s" s="9">
-        <v>1093</v>
+        <v>1104</v>
       </c>
       <c r="J277" t="s" s="15">
-        <v>1094</v>
+        <v>1105</v>
       </c>
       <c r="K277" t="s" s="16">
-        <v>1095</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="278">
@@ -10568,22 +10652,22 @@
         <v>302</v>
       </c>
       <c r="B278" t="s" s="7">
-        <v>1096</v>
+        <v>1107</v>
       </c>
       <c r="C278" t="s" s="8">
-        <v>1097</v>
+        <v>1108</v>
       </c>
       <c r="D278" t="s" s="9">
         <v>47</v>
       </c>
       <c r="E278" t="s" s="10">
-        <v>1098</v>
+        <v>1109</v>
       </c>
       <c r="J278" t="s" s="15">
-        <v>1099</v>
+        <v>1110</v>
       </c>
       <c r="K278" t="s" s="16">
-        <v>1100</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="279">
@@ -10591,19 +10675,19 @@
         <v>303</v>
       </c>
       <c r="B279" t="s" s="7">
-        <v>1101</v>
+        <v>1112</v>
       </c>
       <c r="C279" t="s" s="8">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="D279" t="s" s="9">
-        <v>1103</v>
+        <v>1114</v>
       </c>
       <c r="J279" t="s" s="15">
-        <v>1104</v>
+        <v>1115</v>
       </c>
       <c r="K279" t="s" s="16">
-        <v>1105</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="280">
@@ -10611,19 +10695,19 @@
         <v>304</v>
       </c>
       <c r="B280" t="s" s="7">
-        <v>1106</v>
+        <v>1117</v>
       </c>
       <c r="C280" t="s" s="8">
-        <v>1107</v>
+        <v>1118</v>
       </c>
       <c r="D280" t="s" s="9">
-        <v>1108</v>
+        <v>1119</v>
       </c>
       <c r="J280" t="s" s="15">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="K280" t="s" s="16">
-        <v>1110</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="281">
@@ -10631,25 +10715,25 @@
         <v>305</v>
       </c>
       <c r="B281" t="s" s="7">
-        <v>1111</v>
+        <v>1122</v>
       </c>
       <c r="C281" t="s" s="8">
-        <v>1112</v>
+        <v>1123</v>
       </c>
       <c r="D281" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H281" t="s" s="13">
-        <v>1113</v>
+        <v>1124</v>
       </c>
       <c r="I281" t="s" s="14">
-        <v>1114</v>
+        <v>1125</v>
       </c>
       <c r="J281" t="s" s="15">
-        <v>1115</v>
+        <v>1126</v>
       </c>
       <c r="K281" t="s" s="16">
-        <v>1116</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="282">
@@ -10657,22 +10741,22 @@
         <v>306</v>
       </c>
       <c r="B282" t="s" s="7">
-        <v>1117</v>
+        <v>1128</v>
       </c>
       <c r="C282" t="s" s="8">
-        <v>1118</v>
+        <v>1129</v>
       </c>
       <c r="D282" t="s" s="9">
-        <v>1119</v>
+        <v>1130</v>
       </c>
       <c r="E282" t="s" s="10">
-        <v>1120</v>
+        <v>1131</v>
       </c>
       <c r="J282" t="s" s="15">
-        <v>1121</v>
+        <v>1132</v>
       </c>
       <c r="K282" t="s" s="16">
-        <v>1122</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="283">
@@ -10680,19 +10764,19 @@
         <v>307</v>
       </c>
       <c r="B283" t="s" s="7">
-        <v>1123</v>
+        <v>1134</v>
       </c>
       <c r="C283" t="s" s="8">
-        <v>1124</v>
+        <v>1135</v>
       </c>
       <c r="D283" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J283" t="s" s="15">
-        <v>1125</v>
+        <v>1136</v>
       </c>
       <c r="K283" t="s" s="16">
-        <v>1126</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="284">
@@ -10700,22 +10784,22 @@
         <v>308</v>
       </c>
       <c r="B284" t="s" s="7">
-        <v>1127</v>
+        <v>1138</v>
       </c>
       <c r="C284" t="s" s="8">
-        <v>1128</v>
+        <v>1139</v>
       </c>
       <c r="D284" t="s" s="9">
-        <v>1129</v>
+        <v>1140</v>
       </c>
       <c r="E284" t="s" s="10">
-        <v>1130</v>
+        <v>1141</v>
       </c>
       <c r="J284" t="s" s="15">
-        <v>1131</v>
+        <v>1142</v>
       </c>
       <c r="K284" t="s" s="16">
-        <v>1132</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="285">
@@ -10723,25 +10807,25 @@
         <v>309</v>
       </c>
       <c r="B285" t="s" s="7">
-        <v>1133</v>
+        <v>1144</v>
       </c>
       <c r="C285" t="s" s="8">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="D285" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F285" t="s" s="11">
-        <v>1135</v>
+        <v>1146</v>
       </c>
       <c r="G285" t="s" s="12">
-        <v>1136</v>
+        <v>1147</v>
       </c>
       <c r="J285" t="s" s="15">
-        <v>1137</v>
+        <v>1148</v>
       </c>
       <c r="K285" t="s" s="16">
-        <v>1138</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="286">
@@ -10749,19 +10833,19 @@
         <v>310</v>
       </c>
       <c r="B286" t="s" s="7">
-        <v>1139</v>
+        <v>1150</v>
       </c>
       <c r="C286" t="s" s="8">
-        <v>1140</v>
+        <v>1151</v>
       </c>
       <c r="D286" t="s" s="9">
-        <v>1141</v>
+        <v>1152</v>
       </c>
       <c r="J286" t="s" s="15">
-        <v>1142</v>
+        <v>1153</v>
       </c>
       <c r="K286" t="s" s="16">
-        <v>1143</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="287">
@@ -10769,19 +10853,19 @@
         <v>311</v>
       </c>
       <c r="B287" t="s" s="7">
-        <v>1144</v>
+        <v>1155</v>
       </c>
       <c r="C287" t="s" s="8">
-        <v>1145</v>
+        <v>1156</v>
       </c>
       <c r="D287" t="s" s="9">
-        <v>1146</v>
+        <v>1157</v>
       </c>
       <c r="J287" t="s" s="15">
-        <v>1147</v>
+        <v>1158</v>
       </c>
       <c r="K287" t="s" s="16">
-        <v>1148</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="288">
@@ -10789,28 +10873,28 @@
         <v>312</v>
       </c>
       <c r="B288" t="s" s="7">
-        <v>1149</v>
+        <v>1160</v>
       </c>
       <c r="C288" t="s" s="8">
-        <v>1150</v>
+        <v>1161</v>
       </c>
       <c r="D288" t="s" s="9">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="E288" t="s" s="10">
-        <v>1152</v>
+        <v>1163</v>
       </c>
       <c r="F288" t="s" s="11">
-        <v>1153</v>
+        <v>1164</v>
       </c>
       <c r="G288" t="s" s="12">
-        <v>1154</v>
+        <v>1165</v>
       </c>
       <c r="J288" t="s" s="15">
-        <v>1149</v>
+        <v>1160</v>
       </c>
       <c r="K288" t="s" s="16">
-        <v>1155</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="289">
@@ -10818,19 +10902,19 @@
         <v>313</v>
       </c>
       <c r="B289" t="s" s="7">
-        <v>1156</v>
+        <v>1167</v>
       </c>
       <c r="C289" t="s" s="8">
-        <v>1157</v>
+        <v>1168</v>
       </c>
       <c r="D289" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J289" t="s" s="15">
-        <v>1158</v>
+        <v>1169</v>
       </c>
       <c r="K289" t="s" s="16">
-        <v>1159</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="290">
@@ -10838,10 +10922,10 @@
         <v>314</v>
       </c>
       <c r="B290" t="s" s="7">
-        <v>1160</v>
+        <v>1171</v>
       </c>
       <c r="C290" t="s" s="8">
-        <v>1161</v>
+        <v>1172</v>
       </c>
       <c r="D290" t="s" s="9">
         <v>47</v>
@@ -10852,22 +10936,22 @@
         <v>317</v>
       </c>
       <c r="B291" t="s" s="7">
-        <v>1162</v>
+        <v>1173</v>
       </c>
       <c r="C291" t="s" s="8">
-        <v>1163</v>
+        <v>1174</v>
       </c>
       <c r="D291" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H291" t="s" s="13">
-        <v>1164</v>
+        <v>1175</v>
       </c>
       <c r="I291" t="s" s="14">
-        <v>1165</v>
+        <v>1176</v>
       </c>
       <c r="P291" t="s" s="21">
-        <v>1166</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="292">
@@ -10875,19 +10959,19 @@
         <v>320</v>
       </c>
       <c r="B292" t="s" s="7">
-        <v>1167</v>
+        <v>1178</v>
       </c>
       <c r="C292" t="s" s="8">
-        <v>1168</v>
+        <v>1179</v>
       </c>
       <c r="D292" t="s" s="9">
-        <v>1169</v>
+        <v>1180</v>
       </c>
       <c r="H292" t="s" s="13">
-        <v>1170</v>
+        <v>1181</v>
       </c>
       <c r="I292" t="s" s="14">
-        <v>1171</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="293">
@@ -10895,13 +10979,13 @@
         <v>321</v>
       </c>
       <c r="B293" t="s" s="7">
-        <v>1172</v>
+        <v>1183</v>
       </c>
       <c r="C293" t="s" s="8">
-        <v>1173</v>
+        <v>1184</v>
       </c>
       <c r="D293" t="s" s="9">
-        <v>1174</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="294">
@@ -10909,16 +10993,16 @@
         <v>322</v>
       </c>
       <c r="B294" t="s" s="7">
-        <v>1175</v>
+        <v>1186</v>
       </c>
       <c r="C294" t="s" s="8">
-        <v>1176</v>
+        <v>1187</v>
       </c>
       <c r="D294" t="s" s="9">
-        <v>1177</v>
+        <v>1188</v>
       </c>
       <c r="E294" t="s" s="10">
-        <v>1178</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="295">
@@ -10926,22 +11010,22 @@
         <v>323</v>
       </c>
       <c r="B295" t="s" s="7">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="D295" t="s" s="9">
-        <v>1180</v>
+        <v>1191</v>
       </c>
       <c r="E295" t="s" s="10">
-        <v>1181</v>
+        <v>1192</v>
       </c>
       <c r="J295" t="s" s="15">
-        <v>1182</v>
+        <v>1193</v>
       </c>
       <c r="K295" t="s" s="16">
-        <v>1183</v>
+        <v>1194</v>
       </c>
       <c r="O295" t="s" s="20">
-        <v>1184</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="296">
@@ -10949,16 +11033,16 @@
         <v>324</v>
       </c>
       <c r="B296" t="s" s="7">
-        <v>1185</v>
+        <v>1196</v>
       </c>
       <c r="D296" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H296" t="s" s="13">
-        <v>1185</v>
+        <v>1196</v>
       </c>
       <c r="I296" t="s" s="14">
-        <v>1186</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="297">
@@ -10966,19 +11050,19 @@
         <v>325</v>
       </c>
       <c r="B297" t="s" s="7">
-        <v>1187</v>
+        <v>1198</v>
       </c>
       <c r="D297" t="s" s="9">
-        <v>1188</v>
+        <v>1199</v>
       </c>
       <c r="E297" t="s" s="10">
-        <v>1189</v>
+        <v>1200</v>
       </c>
       <c r="J297" t="s" s="15">
-        <v>1190</v>
+        <v>1201</v>
       </c>
       <c r="K297" t="s" s="16">
-        <v>1191</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="298">
@@ -10986,16 +11070,16 @@
         <v>326</v>
       </c>
       <c r="B298" t="s" s="7">
-        <v>1192</v>
+        <v>1203</v>
       </c>
       <c r="D298" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J298" t="s" s="15">
-        <v>1193</v>
+        <v>1204</v>
       </c>
       <c r="K298" t="s" s="16">
-        <v>1194</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="299">
@@ -11003,16 +11087,16 @@
         <v>327</v>
       </c>
       <c r="B299" t="s" s="7">
-        <v>1195</v>
+        <v>1206</v>
       </c>
       <c r="D299" t="s" s="9">
-        <v>1196</v>
+        <v>1207</v>
       </c>
       <c r="J299" t="s" s="15">
-        <v>1197</v>
+        <v>1208</v>
       </c>
       <c r="K299" t="s" s="16">
-        <v>1198</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="300">
@@ -11020,16 +11104,16 @@
         <v>328</v>
       </c>
       <c r="B300" t="s" s="7">
-        <v>1199</v>
+        <v>1210</v>
       </c>
       <c r="D300" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J300" t="s" s="15">
-        <v>1200</v>
+        <v>1211</v>
       </c>
       <c r="K300" t="s" s="16">
-        <v>1201</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="301">
@@ -11037,16 +11121,16 @@
         <v>329</v>
       </c>
       <c r="B301" t="s" s="7">
-        <v>1202</v>
+        <v>1213</v>
       </c>
       <c r="D301" t="s" s="9">
-        <v>1203</v>
+        <v>1214</v>
       </c>
       <c r="F301" t="s" s="11">
-        <v>1204</v>
+        <v>1215</v>
       </c>
       <c r="G301" t="s" s="12">
-        <v>1205</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="302">
@@ -11054,16 +11138,16 @@
         <v>330</v>
       </c>
       <c r="B302" t="s" s="7">
-        <v>1206</v>
+        <v>1217</v>
       </c>
       <c r="D302" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H302" t="s" s="13">
-        <v>1207</v>
+        <v>1218</v>
       </c>
       <c r="I302" t="s" s="14">
-        <v>1208</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="303">
@@ -11071,16 +11155,16 @@
         <v>331</v>
       </c>
       <c r="B303" t="s" s="7">
-        <v>1209</v>
+        <v>1220</v>
       </c>
       <c r="D303" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H303" t="s" s="13">
-        <v>1210</v>
+        <v>1221</v>
       </c>
       <c r="I303" t="s" s="14">
-        <v>1211</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="304">
@@ -11088,16 +11172,16 @@
         <v>332</v>
       </c>
       <c r="B304" t="s" s="7">
-        <v>1212</v>
+        <v>1223</v>
       </c>
       <c r="D304" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H304" t="s" s="13">
-        <v>1213</v>
+        <v>1224</v>
       </c>
       <c r="I304" t="s" s="14">
-        <v>1214</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="305">
@@ -11105,16 +11189,16 @@
         <v>333</v>
       </c>
       <c r="B305" t="s" s="7">
-        <v>1215</v>
+        <v>1226</v>
       </c>
       <c r="D305" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H305" t="s" s="13">
-        <v>1216</v>
+        <v>1227</v>
       </c>
       <c r="I305" t="s" s="14">
-        <v>1217</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="306">
@@ -11122,16 +11206,16 @@
         <v>334</v>
       </c>
       <c r="B306" t="s" s="7">
-        <v>1218</v>
+        <v>1229</v>
       </c>
       <c r="D306" t="s" s="9">
-        <v>1203</v>
+        <v>1214</v>
       </c>
       <c r="J306" t="s" s="15">
-        <v>1219</v>
+        <v>1230</v>
       </c>
       <c r="K306" t="s" s="16">
-        <v>1220</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="307">
@@ -11139,16 +11223,16 @@
         <v>335</v>
       </c>
       <c r="B307" t="s" s="7">
-        <v>1221</v>
+        <v>1232</v>
       </c>
       <c r="D307" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J307" t="s" s="15">
-        <v>1222</v>
+        <v>1233</v>
       </c>
       <c r="K307" t="s" s="16">
-        <v>1223</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="308">
@@ -11156,16 +11240,16 @@
         <v>336</v>
       </c>
       <c r="B308" t="s" s="7">
-        <v>1224</v>
+        <v>1235</v>
       </c>
       <c r="D308" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J308" t="s" s="15">
-        <v>1224</v>
+        <v>1235</v>
       </c>
       <c r="K308" t="s" s="16">
-        <v>1225</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="309">
@@ -11173,16 +11257,16 @@
         <v>337</v>
       </c>
       <c r="B309" t="s" s="7">
-        <v>1226</v>
+        <v>1237</v>
       </c>
       <c r="D309" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J309" t="s" s="15">
-        <v>1227</v>
+        <v>1238</v>
       </c>
       <c r="K309" t="s" s="16">
-        <v>1228</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="310">
@@ -11190,16 +11274,16 @@
         <v>338</v>
       </c>
       <c r="B310" t="s" s="7">
-        <v>1229</v>
+        <v>1240</v>
       </c>
       <c r="D310" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J310" t="s" s="15">
-        <v>1230</v>
+        <v>1241</v>
       </c>
       <c r="K310" t="s" s="16">
-        <v>1231</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="311">
@@ -11207,25 +11291,25 @@
         <v>339</v>
       </c>
       <c r="B311" t="s" s="7">
-        <v>1232</v>
+        <v>1243</v>
       </c>
       <c r="D311" t="s" s="9">
-        <v>1233</v>
+        <v>1244</v>
       </c>
       <c r="F311" t="s" s="11">
         <v>39</v>
       </c>
       <c r="H311" t="s" s="13">
-        <v>1234</v>
+        <v>1245</v>
       </c>
       <c r="I311" t="s" s="14">
-        <v>1235</v>
+        <v>1246</v>
       </c>
       <c r="J311" t="s" s="15">
-        <v>1236</v>
+        <v>1247</v>
       </c>
       <c r="K311" t="s" s="16">
-        <v>1237</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="312">
@@ -11233,19 +11317,19 @@
         <v>340</v>
       </c>
       <c r="B312" t="s" s="7">
-        <v>1238</v>
+        <v>1249</v>
       </c>
       <c r="D312" t="s" s="9">
-        <v>1239</v>
+        <v>1250</v>
       </c>
       <c r="F312" t="s" s="11">
         <v>39</v>
       </c>
       <c r="J312" t="s" s="15">
-        <v>1240</v>
+        <v>1251</v>
       </c>
       <c r="K312" t="s" s="16">
-        <v>1241</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="313">
@@ -11253,16 +11337,16 @@
         <v>341</v>
       </c>
       <c r="B313" t="s" s="7">
-        <v>1242</v>
+        <v>1253</v>
       </c>
       <c r="D313" t="s" s="9">
-        <v>1243</v>
+        <v>1254</v>
       </c>
       <c r="F313" t="s" s="11">
-        <v>1244</v>
+        <v>1255</v>
       </c>
       <c r="G313" t="s" s="12">
-        <v>1245</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="314">
@@ -11270,19 +11354,19 @@
         <v>342</v>
       </c>
       <c r="B314" t="s" s="7">
-        <v>1246</v>
+        <v>1257</v>
       </c>
       <c r="D314" t="s" s="9">
-        <v>1243</v>
+        <v>1254</v>
       </c>
       <c r="F314" t="s" s="11">
         <v>39</v>
       </c>
       <c r="J314" t="s" s="15">
-        <v>1247</v>
+        <v>1258</v>
       </c>
       <c r="K314" t="s" s="16">
-        <v>1248</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="315">
@@ -11290,16 +11374,16 @@
         <v>343</v>
       </c>
       <c r="B315" t="s" s="7">
-        <v>1249</v>
+        <v>1260</v>
       </c>
       <c r="D315" t="s" s="9">
-        <v>1243</v>
+        <v>1254</v>
       </c>
       <c r="F315" t="s" s="11">
-        <v>1250</v>
+        <v>1261</v>
       </c>
       <c r="G315" t="s" s="12">
-        <v>1251</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="316">
@@ -11307,19 +11391,19 @@
         <v>344</v>
       </c>
       <c r="B316" t="s" s="7">
-        <v>1252</v>
+        <v>1263</v>
       </c>
       <c r="D316" t="s" s="9">
-        <v>1253</v>
+        <v>1264</v>
       </c>
       <c r="E316" t="s" s="10">
-        <v>1254</v>
+        <v>1265</v>
       </c>
       <c r="J316" t="s" s="15">
-        <v>1255</v>
+        <v>1266</v>
       </c>
       <c r="K316" t="s" s="16">
-        <v>1256</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="317">
@@ -11327,19 +11411,19 @@
         <v>345</v>
       </c>
       <c r="B317" t="s" s="7">
-        <v>1257</v>
+        <v>1268</v>
       </c>
       <c r="D317" t="s" s="9">
-        <v>1258</v>
+        <v>1269</v>
       </c>
       <c r="E317" t="s" s="10">
-        <v>1254</v>
+        <v>1265</v>
       </c>
       <c r="J317" t="s" s="15">
-        <v>1259</v>
+        <v>1270</v>
       </c>
       <c r="K317" t="s" s="16">
-        <v>1260</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="318">
@@ -11347,19 +11431,19 @@
         <v>346</v>
       </c>
       <c r="B318" t="s" s="7">
-        <v>1261</v>
+        <v>1272</v>
       </c>
       <c r="D318" t="s" s="9">
-        <v>1262</v>
+        <v>1273</v>
       </c>
       <c r="E318" t="s" s="10">
-        <v>1254</v>
+        <v>1265</v>
       </c>
       <c r="J318" t="s" s="15">
-        <v>1263</v>
+        <v>1274</v>
       </c>
       <c r="K318" t="s" s="16">
-        <v>1264</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="319">
@@ -11367,16 +11451,16 @@
         <v>347</v>
       </c>
       <c r="B319" t="s" s="7">
-        <v>1265</v>
+        <v>1276</v>
       </c>
       <c r="D319" t="s" s="9">
-        <v>1266</v>
+        <v>1277</v>
       </c>
       <c r="H319" t="s" s="13">
-        <v>1267</v>
+        <v>1278</v>
       </c>
       <c r="I319" t="s" s="14">
-        <v>1268</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="320">
@@ -11384,31 +11468,31 @@
         <v>348</v>
       </c>
       <c r="B320" t="s" s="7">
-        <v>1269</v>
+        <v>1280</v>
       </c>
       <c r="D320" t="s" s="9">
-        <v>1270</v>
+        <v>1281</v>
       </c>
       <c r="E320" t="s" s="10">
-        <v>1271</v>
+        <v>1282</v>
       </c>
       <c r="H320" t="s" s="13">
-        <v>1267</v>
+        <v>1278</v>
       </c>
       <c r="I320" t="s" s="14">
-        <v>1268</v>
+        <v>1279</v>
       </c>
       <c r="J320" t="s" s="15">
-        <v>1272</v>
+        <v>1283</v>
       </c>
       <c r="K320" t="s" s="16">
-        <v>1273</v>
+        <v>1284</v>
       </c>
       <c r="N320" t="s" s="19">
-        <v>1274</v>
+        <v>1285</v>
       </c>
       <c r="O320" t="s" s="20">
-        <v>1275</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="321">
@@ -11416,31 +11500,31 @@
         <v>349</v>
       </c>
       <c r="B321" t="s" s="7">
-        <v>1276</v>
+        <v>1287</v>
       </c>
       <c r="C321" t="s" s="8">
-        <v>1277</v>
+        <v>1288</v>
       </c>
       <c r="D321" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F321" t="s" s="11">
-        <v>1278</v>
+        <v>1289</v>
       </c>
       <c r="G321" t="s" s="12">
-        <v>1279</v>
+        <v>1290</v>
       </c>
       <c r="H321" t="s" s="13">
-        <v>1280</v>
+        <v>1291</v>
       </c>
       <c r="I321" t="s" s="14">
-        <v>1281</v>
+        <v>1292</v>
       </c>
       <c r="J321" t="s" s="15">
-        <v>1282</v>
+        <v>1293</v>
       </c>
       <c r="K321" t="s" s="16">
-        <v>1283</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="322">
@@ -11448,16 +11532,16 @@
         <v>350</v>
       </c>
       <c r="B322" t="s" s="7">
-        <v>1284</v>
+        <v>1295</v>
       </c>
       <c r="D322" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J322" t="s" s="15">
-        <v>1285</v>
+        <v>1296</v>
       </c>
       <c r="K322" t="s" s="16">
-        <v>1286</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="323">
@@ -11465,19 +11549,19 @@
         <v>351</v>
       </c>
       <c r="B323" t="s" s="7">
-        <v>1287</v>
+        <v>1298</v>
       </c>
       <c r="D323" t="s" s="9">
-        <v>1288</v>
+        <v>1299</v>
       </c>
       <c r="E323" t="s" s="10">
-        <v>1289</v>
+        <v>1300</v>
       </c>
       <c r="J323" t="s" s="15">
-        <v>1290</v>
+        <v>1301</v>
       </c>
       <c r="K323" t="s" s="16">
-        <v>1291</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="324">
@@ -11485,25 +11569,25 @@
         <v>352</v>
       </c>
       <c r="B324" t="s" s="7">
-        <v>1292</v>
+        <v>1303</v>
       </c>
       <c r="D324" t="s" s="9">
-        <v>1293</v>
+        <v>1304</v>
       </c>
       <c r="E324" t="s" s="10">
-        <v>1294</v>
+        <v>1305</v>
       </c>
       <c r="F324" t="s" s="11">
-        <v>1295</v>
+        <v>1306</v>
       </c>
       <c r="G324" t="s" s="12">
-        <v>1296</v>
+        <v>1307</v>
       </c>
       <c r="N324" t="s" s="19">
-        <v>1297</v>
+        <v>1308</v>
       </c>
       <c r="O324" t="s" s="20">
-        <v>1298</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="325">
@@ -11511,16 +11595,16 @@
         <v>353</v>
       </c>
       <c r="B325" t="s" s="7">
-        <v>1299</v>
+        <v>1310</v>
       </c>
       <c r="D325" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J325" t="s" s="15">
-        <v>1300</v>
+        <v>1311</v>
       </c>
       <c r="K325" t="s" s="16">
-        <v>1301</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="326">
@@ -11528,16 +11612,16 @@
         <v>354</v>
       </c>
       <c r="B326" t="s" s="7">
-        <v>1302</v>
+        <v>1313</v>
       </c>
       <c r="D326" t="s" s="9">
-        <v>1303</v>
+        <v>1314</v>
       </c>
       <c r="F326" t="s" s="11">
-        <v>1304</v>
+        <v>1315</v>
       </c>
       <c r="G326" t="s" s="12">
-        <v>1305</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="327">
@@ -11545,10 +11629,10 @@
         <v>355</v>
       </c>
       <c r="B327" t="s" s="7">
-        <v>1306</v>
+        <v>1317</v>
       </c>
       <c r="D327" t="s" s="9">
-        <v>1307</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="328">
@@ -11556,7 +11640,7 @@
         <v>356</v>
       </c>
       <c r="B328" t="s" s="7">
-        <v>1308</v>
+        <v>1319</v>
       </c>
       <c r="D328" t="s" s="9">
         <v>47</v>
@@ -11567,10 +11651,10 @@
         <v>357</v>
       </c>
       <c r="B329" t="s" s="7">
-        <v>1309</v>
+        <v>1320</v>
       </c>
       <c r="C329" t="s" s="8">
-        <v>1310</v>
+        <v>1321</v>
       </c>
       <c r="D329" t="s" s="9">
         <v>47</v>
@@ -11581,19 +11665,19 @@
         <v>358</v>
       </c>
       <c r="B330" t="s" s="7">
-        <v>1311</v>
+        <v>1322</v>
       </c>
       <c r="C330" t="s" s="8">
-        <v>1312</v>
+        <v>1323</v>
       </c>
       <c r="D330" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F330" t="s" s="11">
-        <v>1313</v>
+        <v>1324</v>
       </c>
       <c r="G330" t="s" s="12">
-        <v>1314</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="331">
@@ -11601,10 +11685,10 @@
         <v>359</v>
       </c>
       <c r="B331" t="s" s="7">
-        <v>1315</v>
+        <v>1326</v>
       </c>
       <c r="C331" t="s" s="8">
-        <v>1316</v>
+        <v>1327</v>
       </c>
       <c r="D331" t="s" s="9">
         <v>47</v>
@@ -11615,22 +11699,22 @@
         <v>360</v>
       </c>
       <c r="B332" t="s" s="7">
-        <v>1317</v>
+        <v>1328</v>
       </c>
       <c r="C332" t="s" s="8">
-        <v>1318</v>
+        <v>1329</v>
       </c>
       <c r="D332" t="s" s="9">
-        <v>1319</v>
+        <v>1330</v>
       </c>
       <c r="E332" t="s" s="10">
-        <v>1320</v>
+        <v>1331</v>
       </c>
       <c r="J332" t="s" s="15">
-        <v>1321</v>
+        <v>1332</v>
       </c>
       <c r="K332" t="s" s="16">
-        <v>1322</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="333">
@@ -11638,19 +11722,19 @@
         <v>361</v>
       </c>
       <c r="B333" t="s" s="7">
-        <v>1323</v>
+        <v>1334</v>
       </c>
       <c r="C333" t="s" s="8">
-        <v>1324</v>
+        <v>1335</v>
       </c>
       <c r="D333" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J333" t="s" s="15">
-        <v>1325</v>
+        <v>1336</v>
       </c>
       <c r="K333" t="s" s="16">
-        <v>1326</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="334">
@@ -11658,10 +11742,10 @@
         <v>362</v>
       </c>
       <c r="B334" t="s" s="7">
-        <v>1327</v>
+        <v>1338</v>
       </c>
       <c r="C334" t="s" s="8">
-        <v>1328</v>
+        <v>1339</v>
       </c>
       <c r="D334" t="s" s="9">
         <v>47</v>
@@ -11672,19 +11756,19 @@
         <v>363</v>
       </c>
       <c r="B335" t="s" s="7">
-        <v>1329</v>
+        <v>1340</v>
       </c>
       <c r="C335" t="s" s="8">
-        <v>1330</v>
+        <v>1341</v>
       </c>
       <c r="D335" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J335" t="s" s="15">
-        <v>1331</v>
+        <v>1342</v>
       </c>
       <c r="K335" t="s" s="16">
-        <v>1332</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="336">
@@ -11692,10 +11776,10 @@
         <v>364</v>
       </c>
       <c r="B336" t="s" s="7">
-        <v>1333</v>
+        <v>1344</v>
       </c>
       <c r="C336" t="s" s="8">
-        <v>1334</v>
+        <v>1345</v>
       </c>
       <c r="D336" t="s" s="9">
         <v>47</v>
@@ -11706,10 +11790,10 @@
         <v>365</v>
       </c>
       <c r="B337" t="s" s="7">
-        <v>1335</v>
+        <v>1346</v>
       </c>
       <c r="C337" t="s" s="8">
-        <v>1336</v>
+        <v>1347</v>
       </c>
       <c r="D337" t="s" s="9">
         <v>47</v>
@@ -11720,22 +11804,22 @@
         <v>366</v>
       </c>
       <c r="B338" t="s" s="7">
-        <v>1337</v>
+        <v>1348</v>
       </c>
       <c r="C338" t="s" s="8">
-        <v>1338</v>
+        <v>1349</v>
       </c>
       <c r="D338" t="s" s="9">
-        <v>1339</v>
+        <v>1350</v>
       </c>
       <c r="E338" t="s" s="10">
-        <v>1340</v>
+        <v>1351</v>
       </c>
       <c r="F338" t="s" s="11">
-        <v>1341</v>
+        <v>1352</v>
       </c>
       <c r="G338" t="s" s="12">
-        <v>1342</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="339">
@@ -11743,16 +11827,16 @@
         <v>367</v>
       </c>
       <c r="B339" t="s" s="7">
-        <v>1343</v>
+        <v>1354</v>
       </c>
       <c r="C339" t="s" s="8">
-        <v>1344</v>
+        <v>1355</v>
       </c>
       <c r="D339" t="s" s="9">
-        <v>1345</v>
+        <v>1356</v>
       </c>
       <c r="E339" t="s" s="10">
-        <v>1346</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="340">
@@ -11760,10 +11844,10 @@
         <v>368</v>
       </c>
       <c r="B340" t="s" s="7">
-        <v>1347</v>
+        <v>1358</v>
       </c>
       <c r="C340" t="s" s="8">
-        <v>1348</v>
+        <v>1359</v>
       </c>
       <c r="D340" t="s" s="9">
         <v>47</v>
@@ -11774,19 +11858,19 @@
         <v>369</v>
       </c>
       <c r="B341" t="s" s="7">
-        <v>1349</v>
+        <v>1360</v>
       </c>
       <c r="C341" t="s" s="8">
-        <v>1350</v>
+        <v>1361</v>
       </c>
       <c r="D341" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J341" t="s" s="15">
-        <v>1351</v>
+        <v>1362</v>
       </c>
       <c r="K341" t="s" s="16">
-        <v>1352</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="342">
@@ -11794,22 +11878,22 @@
         <v>370</v>
       </c>
       <c r="B342" t="s" s="7">
-        <v>1353</v>
+        <v>1364</v>
       </c>
       <c r="D342" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F342" t="s" s="11">
-        <v>1353</v>
+        <v>1364</v>
       </c>
       <c r="G342" t="s" s="12">
-        <v>1354</v>
+        <v>1365</v>
       </c>
       <c r="H342" t="s" s="13">
-        <v>1353</v>
+        <v>1364</v>
       </c>
       <c r="I342" t="s" s="14">
-        <v>1355</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="343">
@@ -11817,28 +11901,28 @@
         <v>372</v>
       </c>
       <c r="B343" t="s" s="7">
-        <v>1356</v>
+        <v>1367</v>
       </c>
       <c r="D343" t="s" s="9">
-        <v>1357</v>
+        <v>1368</v>
       </c>
       <c r="E343" t="s" s="10">
-        <v>1358</v>
+        <v>1369</v>
       </c>
       <c r="F343" t="s" s="11">
-        <v>1359</v>
+        <v>1370</v>
       </c>
       <c r="G343" t="s" s="12">
-        <v>1360</v>
+        <v>1371</v>
       </c>
       <c r="H343" t="s" s="13">
-        <v>1361</v>
+        <v>1372</v>
       </c>
       <c r="I343" t="s" s="14">
-        <v>1362</v>
+        <v>1373</v>
       </c>
       <c r="N343" t="s" s="19">
-        <v>1363</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="344">
@@ -11846,16 +11930,16 @@
         <v>373</v>
       </c>
       <c r="B344" t="s" s="7">
-        <v>1364</v>
+        <v>1375</v>
       </c>
       <c r="D344" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H344" t="s" s="13">
-        <v>1365</v>
+        <v>1376</v>
       </c>
       <c r="I344" t="s" s="14">
-        <v>1366</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="345">
@@ -11863,16 +11947,16 @@
         <v>374</v>
       </c>
       <c r="B345" t="s" s="7">
-        <v>1367</v>
+        <v>1378</v>
       </c>
       <c r="D345" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H345" t="s" s="13">
-        <v>1368</v>
+        <v>1379</v>
       </c>
       <c r="I345" t="s" s="14">
-        <v>1369</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="346">
@@ -11880,16 +11964,16 @@
         <v>375</v>
       </c>
       <c r="B346" t="s" s="7">
-        <v>1370</v>
+        <v>1381</v>
       </c>
       <c r="D346" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H346" t="s" s="13">
-        <v>1371</v>
+        <v>1382</v>
       </c>
       <c r="I346" t="s" s="14">
-        <v>1372</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="347">
@@ -11897,16 +11981,16 @@
         <v>376</v>
       </c>
       <c r="B347" t="s" s="7">
-        <v>1373</v>
+        <v>1384</v>
       </c>
       <c r="D347" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H347" t="s" s="13">
-        <v>1374</v>
+        <v>1385</v>
       </c>
       <c r="I347" t="s" s="14">
-        <v>1375</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="348">
@@ -11914,16 +11998,16 @@
         <v>377</v>
       </c>
       <c r="B348" t="s" s="7">
-        <v>1376</v>
+        <v>1387</v>
       </c>
       <c r="D348" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H348" t="s" s="13">
-        <v>1377</v>
+        <v>1388</v>
       </c>
       <c r="I348" t="s" s="14">
-        <v>1378</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="349">
@@ -11931,16 +12015,16 @@
         <v>378</v>
       </c>
       <c r="B349" t="s" s="7">
-        <v>1379</v>
+        <v>1390</v>
       </c>
       <c r="D349" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H349" t="s" s="13">
-        <v>1380</v>
+        <v>1391</v>
       </c>
       <c r="I349" t="s" s="14">
-        <v>1381</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="350">
@@ -11948,22 +12032,22 @@
         <v>379</v>
       </c>
       <c r="B350" t="s" s="7">
-        <v>1382</v>
+        <v>1393</v>
       </c>
       <c r="D350" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H350" t="s" s="13">
-        <v>1383</v>
+        <v>1394</v>
       </c>
       <c r="I350" t="s" s="14">
-        <v>1384</v>
+        <v>1395</v>
       </c>
       <c r="J350" t="s" s="15">
-        <v>1385</v>
+        <v>1396</v>
       </c>
       <c r="K350" t="s" s="16">
-        <v>1386</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="351">
@@ -11971,19 +12055,19 @@
         <v>380</v>
       </c>
       <c r="B351" t="s" s="7">
-        <v>1387</v>
+        <v>1398</v>
       </c>
       <c r="D351" t="s" s="9">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="E351" t="s" s="10">
-        <v>1389</v>
+        <v>1400</v>
       </c>
       <c r="H351" t="s" s="13">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="I351" t="s" s="14">
-        <v>1391</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="352">
@@ -11991,22 +12075,22 @@
         <v>381</v>
       </c>
       <c r="B352" t="s" s="7">
-        <v>1392</v>
+        <v>1403</v>
       </c>
       <c r="D352" t="s" s="9">
-        <v>1393</v>
+        <v>1404</v>
       </c>
       <c r="F352" t="s" s="11">
-        <v>1394</v>
+        <v>1405</v>
       </c>
       <c r="G352" t="s" s="12">
-        <v>1395</v>
+        <v>1406</v>
       </c>
       <c r="J352" t="s" s="15">
-        <v>1396</v>
+        <v>1407</v>
       </c>
       <c r="K352" t="s" s="16">
-        <v>1397</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="353">
@@ -12014,16 +12098,16 @@
         <v>382</v>
       </c>
       <c r="B353" t="s" s="7">
-        <v>1398</v>
+        <v>1409</v>
       </c>
       <c r="D353" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J353" t="s" s="15">
-        <v>1399</v>
+        <v>1410</v>
       </c>
       <c r="K353" t="s" s="16">
-        <v>1400</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="354">
@@ -12031,16 +12115,16 @@
         <v>383</v>
       </c>
       <c r="B354" t="s" s="7">
-        <v>1401</v>
+        <v>1412</v>
       </c>
       <c r="D354" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J354" t="s" s="15">
-        <v>1402</v>
+        <v>1413</v>
       </c>
       <c r="K354" t="s" s="16">
-        <v>1403</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="355">
@@ -12048,22 +12132,22 @@
         <v>384</v>
       </c>
       <c r="B355" t="s" s="7">
-        <v>1404</v>
+        <v>1415</v>
       </c>
       <c r="D355" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H355" t="s" s="13">
-        <v>1405</v>
+        <v>1416</v>
       </c>
       <c r="I355" t="s" s="14">
-        <v>1406</v>
+        <v>1417</v>
       </c>
       <c r="J355" t="s" s="15">
-        <v>1407</v>
+        <v>1418</v>
       </c>
       <c r="K355" t="s" s="16">
-        <v>1408</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="356">
@@ -12071,22 +12155,22 @@
         <v>385</v>
       </c>
       <c r="B356" t="s" s="7">
-        <v>1409</v>
+        <v>1420</v>
       </c>
       <c r="D356" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F356" t="s" s="11">
-        <v>1410</v>
+        <v>1421</v>
       </c>
       <c r="G356" t="s" s="12">
-        <v>1411</v>
+        <v>1422</v>
       </c>
       <c r="J356" t="s" s="15">
-        <v>1412</v>
+        <v>1423</v>
       </c>
       <c r="K356" t="s" s="16">
-        <v>1413</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="357">
@@ -12094,16 +12178,16 @@
         <v>386</v>
       </c>
       <c r="B357" t="s" s="7">
-        <v>1414</v>
+        <v>1425</v>
       </c>
       <c r="D357" t="s" s="9">
-        <v>1203</v>
+        <v>1214</v>
       </c>
       <c r="J357" t="s" s="15">
-        <v>1415</v>
+        <v>1426</v>
       </c>
       <c r="K357" t="s" s="16">
-        <v>1416</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="358">
@@ -12111,16 +12195,16 @@
         <v>387</v>
       </c>
       <c r="B358" t="s" s="7">
-        <v>1417</v>
+        <v>1428</v>
       </c>
       <c r="D358" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J358" t="s" s="15">
-        <v>1418</v>
+        <v>1429</v>
       </c>
       <c r="K358" t="s" s="16">
-        <v>1419</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="359">
@@ -12128,31 +12212,31 @@
         <v>388</v>
       </c>
       <c r="B359" t="s" s="7">
-        <v>1420</v>
+        <v>1431</v>
       </c>
       <c r="D359" t="s" s="9">
-        <v>1421</v>
+        <v>1432</v>
       </c>
       <c r="E359" t="s" s="10">
-        <v>1422</v>
+        <v>1433</v>
       </c>
       <c r="F359" t="s" s="11">
-        <v>1423</v>
+        <v>1434</v>
       </c>
       <c r="G359" t="s" s="12">
-        <v>1424</v>
+        <v>1435</v>
       </c>
       <c r="H359" t="s" s="13">
-        <v>1425</v>
+        <v>1436</v>
       </c>
       <c r="I359" t="s" s="14">
-        <v>1426</v>
+        <v>1437</v>
       </c>
       <c r="J359" t="s" s="15">
-        <v>1427</v>
+        <v>1438</v>
       </c>
       <c r="K359" t="s" s="16">
-        <v>1428</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="360">
@@ -12160,16 +12244,16 @@
         <v>389</v>
       </c>
       <c r="B360" t="s" s="7">
-        <v>1429</v>
+        <v>1440</v>
       </c>
       <c r="D360" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F360" t="s" s="11">
-        <v>1429</v>
+        <v>1440</v>
       </c>
       <c r="G360" t="s" s="12">
-        <v>1430</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="361">
@@ -12177,16 +12261,16 @@
         <v>390</v>
       </c>
       <c r="B361" t="s" s="7">
-        <v>1431</v>
+        <v>1442</v>
       </c>
       <c r="D361" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H361" t="s" s="13">
-        <v>1432</v>
+        <v>1443</v>
       </c>
       <c r="I361" t="s" s="14">
-        <v>1433</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="362">
@@ -12194,16 +12278,16 @@
         <v>391</v>
       </c>
       <c r="B362" t="s" s="7">
-        <v>1434</v>
+        <v>1445</v>
       </c>
       <c r="D362" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H362" t="s" s="13">
-        <v>1435</v>
+        <v>1446</v>
       </c>
       <c r="I362" t="s" s="14">
-        <v>1436</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="363">
@@ -12211,16 +12295,16 @@
         <v>392</v>
       </c>
       <c r="B363" t="s" s="7">
-        <v>1437</v>
+        <v>1448</v>
       </c>
       <c r="D363" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H363" t="s" s="13">
-        <v>1438</v>
+        <v>1449</v>
       </c>
       <c r="I363" t="s" s="14">
-        <v>1439</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="364">
@@ -12228,16 +12312,16 @@
         <v>393</v>
       </c>
       <c r="B364" t="s" s="7">
-        <v>1440</v>
+        <v>1451</v>
       </c>
       <c r="D364" t="s" s="9">
-        <v>1441</v>
+        <v>1452</v>
       </c>
       <c r="H364" t="s" s="13">
-        <v>1442</v>
+        <v>1453</v>
       </c>
       <c r="I364" t="s" s="14">
-        <v>1443</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="365">
@@ -12245,19 +12329,19 @@
         <v>394</v>
       </c>
       <c r="B365" t="s" s="7">
-        <v>1444</v>
+        <v>1455</v>
       </c>
       <c r="D365" t="s" s="9">
-        <v>1445</v>
+        <v>1456</v>
       </c>
       <c r="E365" t="s" s="10">
-        <v>1446</v>
+        <v>1457</v>
       </c>
       <c r="F365" t="s" s="11">
-        <v>1447</v>
+        <v>1458</v>
       </c>
       <c r="G365" t="s" s="12">
-        <v>1448</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="366">
@@ -12265,16 +12349,16 @@
         <v>395</v>
       </c>
       <c r="B366" t="s" s="7">
-        <v>1449</v>
+        <v>1460</v>
       </c>
       <c r="D366" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H366" t="s" s="13">
-        <v>1450</v>
+        <v>1461</v>
       </c>
       <c r="I366" t="s" s="14">
-        <v>1451</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="367">
@@ -12282,16 +12366,16 @@
         <v>396</v>
       </c>
       <c r="B367" t="s" s="7">
-        <v>1452</v>
+        <v>1463</v>
       </c>
       <c r="D367" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H367" t="s" s="13">
-        <v>1453</v>
+        <v>1464</v>
       </c>
       <c r="I367" t="s" s="14">
-        <v>1454</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="368">
@@ -12299,16 +12383,16 @@
         <v>397</v>
       </c>
       <c r="B368" t="s" s="7">
-        <v>1455</v>
+        <v>1466</v>
       </c>
       <c r="D368" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H368" t="s" s="13">
-        <v>1456</v>
+        <v>1467</v>
       </c>
       <c r="I368" t="s" s="14">
-        <v>1457</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="369">
@@ -12316,19 +12400,19 @@
         <v>398</v>
       </c>
       <c r="B369" t="s" s="7">
-        <v>1458</v>
+        <v>1469</v>
       </c>
       <c r="D369" t="s" s="9">
-        <v>1459</v>
+        <v>1470</v>
       </c>
       <c r="H369" t="s" s="13">
-        <v>1458</v>
+        <v>1469</v>
       </c>
       <c r="I369" t="s" s="14">
-        <v>1460</v>
+        <v>1471</v>
       </c>
       <c r="N369" t="s" s="19">
-        <v>1461</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="370">
@@ -12336,16 +12420,16 @@
         <v>399</v>
       </c>
       <c r="B370" t="s" s="7">
-        <v>1462</v>
+        <v>1473</v>
       </c>
       <c r="D370" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H370" t="s" s="13">
-        <v>1463</v>
+        <v>1474</v>
       </c>
       <c r="I370" t="s" s="14">
-        <v>1464</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="371">
@@ -12353,7 +12437,7 @@
         <v>400</v>
       </c>
       <c r="B371" t="s" s="7">
-        <v>1465</v>
+        <v>1476</v>
       </c>
       <c r="D371" t="s" s="9">
         <v>47</v>
@@ -12364,7 +12448,7 @@
         <v>403</v>
       </c>
       <c r="B372" t="s" s="7">
-        <v>1466</v>
+        <v>1477</v>
       </c>
       <c r="D372" t="s" s="9">
         <v>47</v>
@@ -12375,7 +12459,7 @@
         <v>404</v>
       </c>
       <c r="B373" t="s" s="7">
-        <v>1467</v>
+        <v>1478</v>
       </c>
       <c r="D373" t="s" s="9">
         <v>47</v>
@@ -12386,13 +12470,13 @@
         <v>406</v>
       </c>
       <c r="B374" t="s" s="7">
-        <v>1468</v>
+        <v>1479</v>
       </c>
       <c r="D374" t="s" s="9">
-        <v>1469</v>
+        <v>1480</v>
       </c>
       <c r="N374" t="s" s="19">
-        <v>1470</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="375">
@@ -12400,16 +12484,16 @@
         <v>407</v>
       </c>
       <c r="B375" t="s" s="7">
-        <v>1471</v>
+        <v>1482</v>
       </c>
       <c r="D375" t="s" s="9">
-        <v>1472</v>
+        <v>1483</v>
       </c>
       <c r="E375" t="s" s="10">
-        <v>1473</v>
+        <v>1484</v>
       </c>
       <c r="N375" t="s" s="19">
-        <v>1474</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="376">
@@ -12417,16 +12501,16 @@
         <v>408</v>
       </c>
       <c r="B376" t="s" s="7">
-        <v>1475</v>
+        <v>1486</v>
       </c>
       <c r="D376" t="s" s="9">
-        <v>1476</v>
+        <v>1487</v>
       </c>
       <c r="E376" t="s" s="10">
-        <v>1477</v>
+        <v>1488</v>
       </c>
       <c r="N376" t="s" s="19">
-        <v>1478</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="377">
@@ -12434,10 +12518,10 @@
         <v>410</v>
       </c>
       <c r="B377" t="s" s="7">
-        <v>1479</v>
+        <v>1490</v>
       </c>
       <c r="D377" t="s" s="9">
-        <v>1480</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="378">
@@ -12445,16 +12529,16 @@
         <v>411</v>
       </c>
       <c r="B378" t="s" s="7">
-        <v>1481</v>
+        <v>1492</v>
       </c>
       <c r="D378" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J378" t="s" s="15">
-        <v>1482</v>
+        <v>1493</v>
       </c>
       <c r="K378" t="s" s="16">
-        <v>1483</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="379">
@@ -12462,13 +12546,13 @@
         <v>412</v>
       </c>
       <c r="B379" t="s" s="7">
-        <v>1484</v>
+        <v>1495</v>
       </c>
       <c r="D379" t="s" s="9">
         <v>47</v>
       </c>
       <c r="K379" t="s" s="16">
-        <v>1485</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="380">
@@ -12476,16 +12560,16 @@
         <v>413</v>
       </c>
       <c r="B380" t="s" s="7">
-        <v>1486</v>
+        <v>1497</v>
       </c>
       <c r="D380" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J380" t="s" s="15">
-        <v>1487</v>
+        <v>1498</v>
       </c>
       <c r="K380" t="s" s="16">
-        <v>1488</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="381">
@@ -12493,16 +12577,16 @@
         <v>414</v>
       </c>
       <c r="B381" t="s" s="7">
-        <v>1489</v>
+        <v>1500</v>
       </c>
       <c r="D381" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J381" t="s" s="15">
-        <v>1490</v>
+        <v>1501</v>
       </c>
       <c r="K381" t="s" s="16">
-        <v>1491</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="382">
@@ -12510,10 +12594,10 @@
         <v>415</v>
       </c>
       <c r="B382" t="s" s="7">
-        <v>1492</v>
+        <v>1503</v>
       </c>
       <c r="D382" t="s" s="9">
-        <v>1203</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="383">
@@ -12521,13 +12605,13 @@
         <v>416</v>
       </c>
       <c r="B383" t="s" s="7">
-        <v>1493</v>
+        <v>1504</v>
       </c>
       <c r="D383" t="s" s="9">
-        <v>1494</v>
+        <v>1505</v>
       </c>
       <c r="E383" t="s" s="10">
-        <v>1495</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="384">
@@ -12535,31 +12619,31 @@
         <v>417</v>
       </c>
       <c r="B384" t="s" s="7">
-        <v>1496</v>
+        <v>1507</v>
       </c>
       <c r="D384" t="s" s="9">
-        <v>1497</v>
+        <v>1508</v>
       </c>
       <c r="E384" t="s" s="10">
-        <v>1498</v>
+        <v>1509</v>
       </c>
       <c r="F384" t="s" s="11">
-        <v>1499</v>
+        <v>1510</v>
       </c>
       <c r="G384" t="s" s="12">
-        <v>1500</v>
+        <v>1511</v>
       </c>
       <c r="H384" t="s" s="13">
-        <v>1499</v>
+        <v>1510</v>
       </c>
       <c r="I384" t="s" s="14">
-        <v>1501</v>
+        <v>1512</v>
       </c>
       <c r="N384" t="s" s="19">
-        <v>1502</v>
+        <v>1513</v>
       </c>
       <c r="O384" t="s" s="20">
-        <v>1503</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="385">
@@ -12567,10 +12651,10 @@
         <v>418</v>
       </c>
       <c r="B385" t="s" s="7">
-        <v>1504</v>
+        <v>1515</v>
       </c>
       <c r="D385" t="s" s="9">
-        <v>1505</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="386">
@@ -12578,16 +12662,16 @@
         <v>419</v>
       </c>
       <c r="B386" t="s" s="7">
-        <v>1506</v>
+        <v>1517</v>
       </c>
       <c r="D386" t="s" s="9">
-        <v>1507</v>
+        <v>1518</v>
       </c>
       <c r="E386" t="s" s="10">
-        <v>1508</v>
+        <v>1519</v>
       </c>
       <c r="N386" t="s" s="19">
-        <v>1509</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="387">
@@ -12595,19 +12679,19 @@
         <v>421</v>
       </c>
       <c r="B387" t="s" s="7">
-        <v>1510</v>
+        <v>1521</v>
       </c>
       <c r="D387" t="s" s="9">
-        <v>1511</v>
+        <v>1522</v>
       </c>
       <c r="E387" t="s" s="10">
-        <v>1512</v>
+        <v>1523</v>
       </c>
       <c r="H387" t="s" s="13">
-        <v>1513</v>
+        <v>1524</v>
       </c>
       <c r="I387" t="s" s="14">
-        <v>1514</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="388">
@@ -12615,13 +12699,13 @@
         <v>422</v>
       </c>
       <c r="B388" t="s" s="7">
-        <v>1515</v>
+        <v>1526</v>
       </c>
       <c r="D388" t="s" s="9">
-        <v>1516</v>
+        <v>1527</v>
       </c>
       <c r="E388" t="s" s="10">
-        <v>1517</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="389">
@@ -12629,10 +12713,10 @@
         <v>423</v>
       </c>
       <c r="B389" t="s" s="7">
-        <v>1518</v>
+        <v>1529</v>
       </c>
       <c r="D389" t="s" s="9">
-        <v>1519</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="390">
@@ -12640,10 +12724,10 @@
         <v>424</v>
       </c>
       <c r="B390" t="s" s="7">
-        <v>1520</v>
+        <v>1531</v>
       </c>
       <c r="D390" t="s" s="9">
-        <v>1521</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="391">
@@ -12651,22 +12735,22 @@
         <v>425</v>
       </c>
       <c r="B391" t="s" s="7">
-        <v>1522</v>
+        <v>1533</v>
       </c>
       <c r="D391" t="s" s="9">
-        <v>1523</v>
+        <v>1534</v>
       </c>
       <c r="E391" t="s" s="10">
-        <v>1524</v>
+        <v>1535</v>
       </c>
       <c r="J391" t="s" s="15">
-        <v>1525</v>
+        <v>1536</v>
       </c>
       <c r="K391" t="s" s="16">
-        <v>1526</v>
+        <v>1537</v>
       </c>
       <c r="O391" t="s" s="20">
-        <v>1527</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="392">
@@ -12674,10 +12758,10 @@
         <v>426</v>
       </c>
       <c r="B392" t="s" s="7">
-        <v>1528</v>
+        <v>1539</v>
       </c>
       <c r="D392" t="s" s="9">
-        <v>1529</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="393">
@@ -12685,10 +12769,10 @@
         <v>427</v>
       </c>
       <c r="B393" t="s" s="7">
-        <v>1530</v>
+        <v>1541</v>
       </c>
       <c r="D393" t="s" s="9">
-        <v>1531</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="394">
@@ -12696,7 +12780,7 @@
         <v>428</v>
       </c>
       <c r="B394" t="s" s="7">
-        <v>1532</v>
+        <v>1543</v>
       </c>
       <c r="D394" t="s" s="9">
         <v>47</v>
@@ -12707,25 +12791,25 @@
         <v>429</v>
       </c>
       <c r="B395" t="s" s="7">
-        <v>1533</v>
+        <v>1544</v>
       </c>
       <c r="D395" t="s" s="9">
-        <v>1534</v>
+        <v>1545</v>
       </c>
       <c r="E395" t="s" s="10">
-        <v>1535</v>
+        <v>1546</v>
       </c>
       <c r="F395" t="s" s="11">
-        <v>1536</v>
+        <v>1547</v>
       </c>
       <c r="G395" t="s" s="12">
-        <v>1537</v>
+        <v>1548</v>
       </c>
       <c r="H395" t="s" s="13">
-        <v>1536</v>
+        <v>1547</v>
       </c>
       <c r="I395" t="s" s="14">
-        <v>1538</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="396">
@@ -12733,22 +12817,22 @@
         <v>430</v>
       </c>
       <c r="B396" t="s" s="7">
-        <v>1539</v>
+        <v>1550</v>
       </c>
       <c r="D396" t="s" s="9">
-        <v>1540</v>
+        <v>1551</v>
       </c>
       <c r="F396" t="s" s="11">
-        <v>1541</v>
+        <v>1552</v>
       </c>
       <c r="G396" t="s" s="12">
-        <v>1542</v>
+        <v>1553</v>
       </c>
       <c r="H396" t="s" s="13">
-        <v>1541</v>
+        <v>1552</v>
       </c>
       <c r="I396" t="s" s="14">
-        <v>1543</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="397">
@@ -12756,22 +12840,22 @@
         <v>431</v>
       </c>
       <c r="B397" t="s" s="7">
-        <v>1544</v>
+        <v>1555</v>
       </c>
       <c r="D397" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F397" t="s" s="11">
-        <v>1545</v>
+        <v>1556</v>
       </c>
       <c r="G397" t="s" s="12">
-        <v>1546</v>
+        <v>1557</v>
       </c>
       <c r="H397" t="s" s="13">
-        <v>1544</v>
+        <v>1555</v>
       </c>
       <c r="I397" t="s" s="14">
-        <v>1547</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="398">
@@ -12779,7 +12863,7 @@
         <v>432</v>
       </c>
       <c r="B398" t="s" s="7">
-        <v>1548</v>
+        <v>1559</v>
       </c>
       <c r="D398" t="s" s="9">
         <v>47</v>
@@ -12791,10 +12875,10 @@
         <v>246</v>
       </c>
       <c r="H398" t="s" s="13">
-        <v>1549</v>
+        <v>1560</v>
       </c>
       <c r="I398" t="s" s="14">
-        <v>1550</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="399">
@@ -12802,7 +12886,7 @@
         <v>433</v>
       </c>
       <c r="B399" t="s" s="7">
-        <v>1551</v>
+        <v>1562</v>
       </c>
       <c r="D399" t="s" s="9">
         <v>47</v>
@@ -12813,7 +12897,7 @@
         <v>434</v>
       </c>
       <c r="B400" t="s" s="7">
-        <v>1552</v>
+        <v>1563</v>
       </c>
       <c r="D400" t="s" s="9">
         <v>47</v>
@@ -12824,16 +12908,16 @@
         <v>435</v>
       </c>
       <c r="B401" t="s" s="7">
-        <v>1553</v>
+        <v>1564</v>
       </c>
       <c r="D401" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H401" t="s" s="13">
-        <v>1554</v>
+        <v>1565</v>
       </c>
       <c r="I401" t="s" s="14">
-        <v>1555</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="402">
@@ -12841,16 +12925,16 @@
         <v>436</v>
       </c>
       <c r="B402" t="s" s="7">
-        <v>1556</v>
+        <v>1567</v>
       </c>
       <c r="D402" t="s" s="9">
-        <v>1557</v>
+        <v>1568</v>
       </c>
       <c r="J402" t="s" s="15">
-        <v>1558</v>
+        <v>1569</v>
       </c>
       <c r="K402" t="s" s="16">
-        <v>1559</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="403">
@@ -12858,7 +12942,7 @@
         <v>438</v>
       </c>
       <c r="B403" t="s" s="7">
-        <v>1560</v>
+        <v>1571</v>
       </c>
       <c r="D403" t="s" s="9">
         <v>47</v>
@@ -12869,22 +12953,22 @@
         <v>439</v>
       </c>
       <c r="B404" t="s" s="7">
-        <v>1561</v>
+        <v>1572</v>
       </c>
       <c r="D404" t="s" s="9">
-        <v>1562</v>
+        <v>1573</v>
       </c>
       <c r="E404" t="s" s="10">
-        <v>1563</v>
+        <v>1574</v>
       </c>
       <c r="J404" t="s" s="15">
-        <v>1564</v>
+        <v>1575</v>
       </c>
       <c r="K404" t="s" s="16">
-        <v>1565</v>
+        <v>1576</v>
       </c>
       <c r="N404" t="s" s="19">
-        <v>1566</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="405">
@@ -12892,16 +12976,16 @@
         <v>440</v>
       </c>
       <c r="B405" t="s" s="7">
-        <v>1567</v>
+        <v>1578</v>
       </c>
       <c r="D405" t="s" s="9">
         <v>47</v>
       </c>
       <c r="J405" t="s" s="15">
-        <v>1568</v>
+        <v>1579</v>
       </c>
       <c r="K405" t="s" s="16">
-        <v>1569</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="406">
@@ -12909,22 +12993,22 @@
         <v>441</v>
       </c>
       <c r="B406" t="s" s="7">
-        <v>1570</v>
+        <v>1581</v>
       </c>
       <c r="D406" t="s" s="9">
         <v>47</v>
       </c>
       <c r="F406" t="s" s="11">
-        <v>1571</v>
+        <v>1582</v>
       </c>
       <c r="G406" t="s" s="12">
-        <v>1572</v>
+        <v>1583</v>
       </c>
       <c r="H406" t="s" s="13">
-        <v>1571</v>
+        <v>1582</v>
       </c>
       <c r="I406" t="s" s="14">
-        <v>1573</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="407">
@@ -12932,7 +13016,7 @@
         <v>442</v>
       </c>
       <c r="B407" t="s" s="7">
-        <v>1574</v>
+        <v>1585</v>
       </c>
       <c r="D407" t="s" s="9">
         <v>47</v>
@@ -12943,16 +13027,16 @@
         <v>443</v>
       </c>
       <c r="B408" t="s" s="7">
-        <v>1575</v>
+        <v>1586</v>
       </c>
       <c r="D408" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H408" t="s" s="13">
-        <v>1576</v>
+        <v>1587</v>
       </c>
       <c r="I408" t="s" s="14">
-        <v>1577</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="409">
@@ -12960,19 +13044,19 @@
         <v>444</v>
       </c>
       <c r="B409" t="s" s="7">
-        <v>1578</v>
+        <v>1589</v>
       </c>
       <c r="D409" t="s" s="9">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="H409" t="s" s="13">
-        <v>1578</v>
+        <v>1589</v>
       </c>
       <c r="I409" t="s" s="14">
-        <v>1580</v>
+        <v>1591</v>
       </c>
       <c r="N409" t="s" s="19">
-        <v>1581</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="410">
@@ -12980,16 +13064,16 @@
         <v>445</v>
       </c>
       <c r="B410" t="s" s="7">
-        <v>1582</v>
+        <v>1593</v>
       </c>
       <c r="D410" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H410" t="s" s="13">
-        <v>1583</v>
+        <v>1594</v>
       </c>
       <c r="I410" t="s" s="14">
-        <v>1584</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="411">
@@ -12997,16 +13081,16 @@
         <v>446</v>
       </c>
       <c r="B411" t="s" s="7">
-        <v>1585</v>
+        <v>1596</v>
       </c>
       <c r="D411" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H411" t="s" s="13">
-        <v>1586</v>
+        <v>1597</v>
       </c>
       <c r="I411" t="s" s="14">
-        <v>1587</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="412">
@@ -13014,16 +13098,16 @@
         <v>447</v>
       </c>
       <c r="B412" t="s" s="7">
-        <v>1588</v>
+        <v>1599</v>
       </c>
       <c r="D412" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H412" t="s" s="13">
-        <v>1589</v>
+        <v>1600</v>
       </c>
       <c r="I412" t="s" s="14">
-        <v>1590</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="413">
@@ -13031,16 +13115,16 @@
         <v>448</v>
       </c>
       <c r="B413" t="s" s="7">
-        <v>1591</v>
+        <v>1602</v>
       </c>
       <c r="D413" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H413" t="s" s="13">
-        <v>1592</v>
+        <v>1603</v>
       </c>
       <c r="I413" t="s" s="14">
-        <v>1593</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="414">
@@ -13048,16 +13132,16 @@
         <v>449</v>
       </c>
       <c r="B414" t="s" s="7">
-        <v>1594</v>
+        <v>1605</v>
       </c>
       <c r="D414" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H414" t="s" s="13">
-        <v>1594</v>
+        <v>1605</v>
       </c>
       <c r="I414" t="s" s="14">
-        <v>1595</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="415">
@@ -13065,7 +13149,7 @@
         <v>450</v>
       </c>
       <c r="B415" t="s" s="7">
-        <v>1596</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="416">
@@ -13073,19 +13157,19 @@
         <v>451</v>
       </c>
       <c r="B416" t="s" s="7">
-        <v>1597</v>
+        <v>1608</v>
       </c>
       <c r="H416" t="s" s="13">
-        <v>1598</v>
+        <v>1609</v>
       </c>
       <c r="I416" t="s" s="14">
-        <v>1599</v>
+        <v>1610</v>
       </c>
       <c r="J416" t="s" s="15">
-        <v>1600</v>
+        <v>1611</v>
       </c>
       <c r="K416" t="s" s="16">
-        <v>1601</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="417">
@@ -13098,13 +13182,13 @@
         <v>453</v>
       </c>
       <c r="B418" t="s" s="7">
-        <v>1602</v>
+        <v>1613</v>
       </c>
       <c r="J418" t="s" s="15">
-        <v>1603</v>
+        <v>1614</v>
       </c>
       <c r="K418" t="s" s="16">
-        <v>1604</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="419">
@@ -13112,13 +13196,13 @@
         <v>455</v>
       </c>
       <c r="B419" t="s" s="7">
-        <v>1605</v>
+        <v>1616</v>
       </c>
       <c r="H419" t="s" s="13">
-        <v>1605</v>
+        <v>1616</v>
       </c>
       <c r="I419" t="s" s="14">
-        <v>1606</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="420">
@@ -13126,19 +13210,19 @@
         <v>457</v>
       </c>
       <c r="B420" t="s" s="7">
-        <v>1607</v>
+        <v>1618</v>
       </c>
       <c r="D420" t="s" s="9">
-        <v>1608</v>
+        <v>1619</v>
       </c>
       <c r="E420" t="s" s="10">
-        <v>1609</v>
+        <v>1620</v>
       </c>
       <c r="H420" t="s" s="13">
-        <v>1610</v>
+        <v>1621</v>
       </c>
       <c r="I420" t="s" s="14">
-        <v>1611</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="421">
@@ -13146,13 +13230,13 @@
         <v>458</v>
       </c>
       <c r="B421" t="s" s="7">
-        <v>1612</v>
+        <v>1623</v>
       </c>
       <c r="H421" t="s" s="13">
-        <v>1613</v>
+        <v>1624</v>
       </c>
       <c r="I421" t="s" s="14">
-        <v>1614</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="422">
@@ -13160,13 +13244,13 @@
         <v>459</v>
       </c>
       <c r="B422" t="s" s="7">
-        <v>1615</v>
+        <v>1626</v>
       </c>
       <c r="H422" t="s" s="13">
-        <v>1616</v>
+        <v>1627</v>
       </c>
       <c r="I422" t="s" s="14">
-        <v>1617</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="423">
@@ -13174,13 +13258,13 @@
         <v>460</v>
       </c>
       <c r="B423" t="s" s="7">
-        <v>1618</v>
+        <v>1629</v>
       </c>
       <c r="H423" t="s" s="13">
-        <v>1618</v>
+        <v>1629</v>
       </c>
       <c r="I423" t="s" s="14">
-        <v>1619</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="424">
@@ -13188,13 +13272,13 @@
         <v>461</v>
       </c>
       <c r="B424" t="s" s="7">
-        <v>1620</v>
+        <v>1631</v>
       </c>
       <c r="H424" t="s" s="13">
-        <v>1621</v>
+        <v>1632</v>
       </c>
       <c r="I424" t="s" s="14">
-        <v>1622</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="425">
@@ -13202,16 +13286,16 @@
         <v>462</v>
       </c>
       <c r="B425" t="s" s="7">
-        <v>1623</v>
+        <v>1634</v>
       </c>
       <c r="D425" t="s" s="9">
         <v>47</v>
       </c>
       <c r="H425" t="s" s="13">
-        <v>1624</v>
+        <v>1635</v>
       </c>
       <c r="I425" t="s" s="14">
-        <v>1625</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="426">
@@ -13219,13 +13303,13 @@
         <v>463</v>
       </c>
       <c r="B426" t="s" s="7">
-        <v>1626</v>
+        <v>1637</v>
       </c>
       <c r="H426" t="s" s="13">
-        <v>1627</v>
+        <v>1638</v>
       </c>
       <c r="I426" t="s" s="14">
-        <v>1628</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="427">
@@ -13233,7 +13317,7 @@
         <v>464</v>
       </c>
       <c r="B427" t="s" s="7">
-        <v>1629</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="428">
@@ -13241,13 +13325,13 @@
         <v>465</v>
       </c>
       <c r="B428" t="s" s="7">
-        <v>1630</v>
+        <v>1641</v>
       </c>
       <c r="H428" t="s" s="13">
-        <v>1631</v>
+        <v>1642</v>
       </c>
       <c r="I428" t="s" s="14">
-        <v>1632</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="429">
@@ -13255,13 +13339,13 @@
         <v>466</v>
       </c>
       <c r="B429" t="s" s="7">
-        <v>1633</v>
+        <v>1644</v>
       </c>
       <c r="E429" t="s" s="10">
-        <v>1634</v>
+        <v>1645</v>
       </c>
       <c r="O429" t="s" s="20">
-        <v>1635</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="430">
@@ -13269,7 +13353,7 @@
         <v>467</v>
       </c>
       <c r="B430" t="s" s="7">
-        <v>1636</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="431">
@@ -13277,10 +13361,10 @@
         <v>468</v>
       </c>
       <c r="B431" t="s" s="7">
-        <v>1637</v>
+        <v>1648</v>
       </c>
       <c r="C431" t="s" s="8">
-        <v>1638</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="432">
@@ -13288,10 +13372,46 @@
         <v>469</v>
       </c>
       <c r="B432" t="s" s="7">
-        <v>1639</v>
+        <v>1650</v>
       </c>
       <c r="C432" t="s" s="8">
-        <v>1640</v>
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="6">
+        <v>472</v>
+      </c>
+      <c r="B433" t="s" s="7">
+        <v>1652</v>
+      </c>
+      <c r="D433" t="s" s="9">
+        <v>1653</v>
+      </c>
+      <c r="E433" t="s" s="10">
+        <v>1654</v>
+      </c>
+      <c r="O433" t="s" s="20">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="6">
+        <v>473</v>
+      </c>
+      <c r="B434" t="s" s="7">
+        <v>1656</v>
+      </c>
+      <c r="D434" t="s" s="9">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="6">
+        <v>474</v>
+      </c>
+      <c r="B435" t="s" s="7">
+        <v>1658</v>
       </c>
     </row>
   </sheetData>
